--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_37.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_11_37.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3531157.855311145</v>
+        <v>3491652.749273415</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7264945.184841476</v>
+        <v>7259912.105970344</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7264945.184841476</v>
+        <v>7259912.105970344</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4277963.907998742</v>
+        <v>4273330.232798742</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4277963.907998742</v>
+        <v>4273330.232798742</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53516816.6223921</v>
+        <v>53517943.30172174</v>
       </c>
     </row>
   </sheetData>
@@ -663,13 +663,13 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
-        <v>4.363289606868648</v>
+        <v>75.53927021999755</v>
       </c>
       <c r="F2" t="n">
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>78.71767048808493</v>
+        <v>403.6608898749559</v>
       </c>
       <c r="H2" t="n">
         <v>407.0215582010148</v>
@@ -678,13 +678,13 @@
         <v>146.3615214917299</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>288.3590620719278</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>75.85195785378498</v>
       </c>
       <c r="L2" t="n">
-        <v>56.24380582543748</v>
+        <v>14.47071152779773</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -705,10 +705,10 @@
         <v>244.8179355117115</v>
       </c>
       <c r="S2" t="n">
-        <v>492.6495748374988</v>
+        <v>92.64957483749879</v>
       </c>
       <c r="T2" t="n">
-        <v>586.2532299697699</v>
+        <v>186.2532299697699</v>
       </c>
       <c r="U2" t="n">
         <v>249.2135779556459</v>
@@ -723,7 +723,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y2" t="n">
-        <v>111.3174326828064</v>
+        <v>511.3174326828064</v>
       </c>
     </row>
     <row r="3">
@@ -745,13 +745,13 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>212.2400929580573</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>215.3490274007825</v>
@@ -781,10 +781,10 @@
         <v>166.4896801848192</v>
       </c>
       <c r="R3" t="n">
-        <v>144.0686652169076</v>
+        <v>295.9450005128418</v>
       </c>
       <c r="S3" t="n">
-        <v>65.60513204008299</v>
+        <v>465.605132040083</v>
       </c>
       <c r="T3" t="n">
         <v>5.149689745815692</v>
@@ -891,16 +891,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>481.9993129555745</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
         <v>449.4745782429939</v>
       </c>
       <c r="D5" t="n">
-        <v>10.33915573984979</v>
+        <v>410.3391557398498</v>
       </c>
       <c r="E5" t="n">
-        <v>4.363289606868648</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F5" t="n">
         <v>4.889628708011855</v>
@@ -921,13 +921,13 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>56.24380582542908</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>378.6817314535427</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -951,10 +951,10 @@
         <v>249.2135779556459</v>
       </c>
       <c r="V5" t="n">
-        <v>629.8510241668239</v>
+        <v>301.0270047799527</v>
       </c>
       <c r="W5" t="n">
-        <v>313.430256594076</v>
+        <v>238.3734759809475</v>
       </c>
       <c r="X5" t="n">
         <v>192.2818334606677</v>
@@ -979,7 +979,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>215.3490274007825</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>166.4896801848192</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>511.2940279136244</v>
+        <v>144.0686652169076</v>
       </c>
       <c r="S6" t="n">
-        <v>465.605132040083</v>
+        <v>65.60513204008299</v>
       </c>
       <c r="T6" t="n">
         <v>5.149689745815692</v>
@@ -1036,7 +1036,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>19.86273944538755</v>
+        <v>395.5566577042283</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1131,7 +1131,7 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
-        <v>369.3492943678348</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D8" t="n">
         <v>10.33915573984979</v>
@@ -1143,25 +1143,25 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>403.6608898749559</v>
+        <v>3.660889874955899</v>
       </c>
       <c r="H8" t="n">
         <v>7.021558201014841</v>
       </c>
       <c r="I8" t="n">
-        <v>146.3615214917299</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>75.85195785378505</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>302.8297735997657</v>
       </c>
       <c r="M8" t="n">
-        <v>56.24380582540201</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1176,19 +1176,19 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>244.8179355117115</v>
       </c>
       <c r="S8" t="n">
-        <v>92.64957483749879</v>
+        <v>492.6495748374988</v>
       </c>
       <c r="T8" t="n">
-        <v>586.2532299697699</v>
+        <v>186.2532299697699</v>
       </c>
       <c r="U8" t="n">
-        <v>249.2135779556459</v>
+        <v>466.7510800605047</v>
       </c>
       <c r="V8" t="n">
-        <v>229.8510241668239</v>
+        <v>629.8510241668239</v>
       </c>
       <c r="W8" t="n">
         <v>238.3734759809475</v>
@@ -1216,19 +1216,19 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>194.0788005436592</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>331.6695211486853</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>202.0455217328505</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>144.0686652169076</v>
+        <v>544.0686652169076</v>
       </c>
       <c r="S9" t="n">
         <v>65.60513204008299</v>
@@ -1270,7 +1270,7 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>432.3731429098285</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>260.9993129555745</v>
+        <v>124.814224512028</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>228.4745782429939</v>
       </c>
       <c r="D11" t="n">
         <v>189.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>183.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>183.8896287080119</v>
@@ -1419,7 +1419,7 @@
         <v>271.6495748374988</v>
       </c>
       <c r="T11" t="n">
-        <v>365.2532299697699</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
         <v>428.2135779556459</v>
@@ -1431,10 +1431,10 @@
         <v>417.3734759809475</v>
       </c>
       <c r="X11" t="n">
-        <v>209.1530363662827</v>
+        <v>371.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>290.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>7.386339216372718</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1559,7 +1559,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>330.7768086485281</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>318.0176595934456</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>5.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1620,7 +1620,7 @@
         <v>158.6608898749559</v>
       </c>
       <c r="H14" t="n">
-        <v>5.539629278252814</v>
+        <v>162.0215582010148</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>247.6495748374988</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>341.2532299697699</v>
@@ -1662,13 +1662,13 @@
         <v>404.2135779556459</v>
       </c>
       <c r="V14" t="n">
-        <v>384.8510241668239</v>
+        <v>128.736836620893</v>
       </c>
       <c r="W14" t="n">
         <v>393.3734759809475</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>347.2818334606677</v>
       </c>
       <c r="Y14" t="n">
         <v>266.3174326828064</v>
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>38.49257707983156</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1799,16 +1799,16 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>389.3283181773756</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>55.10747140243467</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>477.215266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>5.713100234043905</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1854,10 +1854,10 @@
         <v>123.8896287080119</v>
       </c>
       <c r="G17" t="n">
-        <v>122.6608898749559</v>
+        <v>122.8971274915263</v>
       </c>
       <c r="H17" t="n">
-        <v>126.2577958175852</v>
+        <v>126.0215582010148</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1933,10 +1933,10 @@
         <v>58.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>44.68791323351791</v>
+        <v>44.68791323351792</v>
       </c>
       <c r="H18" t="n">
-        <v>50.66952114868528</v>
+        <v>50.66952114868531</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2024,25 +2024,25 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>2.492577079831563</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>136.1132675020415</v>
       </c>
       <c r="M19" t="n">
-        <v>232.8474802550089</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>224.031055727583</v>
+        <v>235.3708973121596</v>
       </c>
       <c r="O19" t="n">
-        <v>353.3283181773756</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>441.215266425598</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         <v>126.0215582010148</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.2362376165704005</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>211.8858124540692</v>
+        <v>211.6495748374988</v>
       </c>
       <c r="T20" t="n">
         <v>305.2532299697699</v>
@@ -2261,7 +2261,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>2.492577079831563</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2270,22 +2270,22 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>52.04377605280512</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>353.3283181773756</v>
       </c>
       <c r="P22" t="n">
-        <v>275.7931843531699</v>
+        <v>401.2135366725398</v>
       </c>
       <c r="Q22" t="n">
-        <v>441.215266425598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>80.61925019465872</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>6.465352849462363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2334,7 +2334,7 @@
         <v>126.0215582010148</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.2362376165704005</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2362376165704427</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>211.6495748374988</v>
@@ -2407,10 +2407,10 @@
         <v>58.63624233787687</v>
       </c>
       <c r="G24" t="n">
-        <v>44.68791323351792</v>
+        <v>44.68791323351791</v>
       </c>
       <c r="H24" t="n">
-        <v>50.66952114868531</v>
+        <v>50.66952114868528</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2471,13 +2471,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>6.113800337078658</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>4.53621805555548</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -2501,25 +2501,25 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>136.1132675020415</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>232.8474802550089</v>
       </c>
       <c r="N25" t="n">
-        <v>283.5622555995537</v>
+        <v>283.5622555995538</v>
       </c>
       <c r="O25" t="n">
-        <v>353.3283181773756</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>149.5264094905608</v>
       </c>
       <c r="R25" t="n">
-        <v>169.3435046134074</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2540,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>6.465352849462363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>260.9993129555745</v>
       </c>
       <c r="C26" t="n">
         <v>228.4745782429939</v>
@@ -2562,7 +2562,7 @@
         <v>183.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>183.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>182.6608898749559</v>
@@ -2598,22 +2598,22 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>23.81793551171154</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>271.6495748374988</v>
       </c>
       <c r="T26" t="n">
         <v>365.2532299697699</v>
       </c>
       <c r="U26" t="n">
-        <v>428.2135779556459</v>
+        <v>220.5024784621904</v>
       </c>
       <c r="V26" t="n">
         <v>408.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>113.3494240798941</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>371.2818334606677</v>
@@ -2686,7 +2686,7 @@
         <v>184.1496897458157</v>
       </c>
       <c r="U27" t="n">
-        <v>179.2069635337716</v>
+        <v>179.2069635337717</v>
       </c>
       <c r="V27" t="n">
         <v>193.5106671915202</v>
@@ -2708,16 +2708,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>66.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>51.72524664804467</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>59.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -2726,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>7.386339216372718</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2744,10 +2744,10 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>229.793174769698</v>
       </c>
       <c r="O28" t="n">
-        <v>197.2957642581202</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2777,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>49.25838723078537</v>
       </c>
     </row>
     <row r="29">
@@ -2793,7 +2793,7 @@
         <v>157.4745782429939</v>
       </c>
       <c r="D29" t="n">
-        <v>113.4625933564196</v>
+        <v>118.3391557398498</v>
       </c>
       <c r="E29" t="n">
         <v>112.3632896068686</v>
@@ -2814,10 +2814,10 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>35.85195785378517</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>40.8239017356954</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -2850,7 +2850,7 @@
         <v>337.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>346.3734759809475</v>
+        <v>345.3777135975175</v>
       </c>
       <c r="X29" t="n">
         <v>300.2818334606677</v>
@@ -2881,10 +2881,10 @@
         <v>47.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>33.68791323351791</v>
+        <v>33.68791323351792</v>
       </c>
       <c r="H30" t="n">
-        <v>39.66952114868528</v>
+        <v>39.66952114868531</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2978,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>145.55047799134</v>
+        <v>221.8474802550089</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -2987,13 +2987,13 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>390.2135366725398</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>430.215266425598</v>
+        <v>311.4756400664324</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>432.6561607680363</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3051,10 +3051,10 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>35.85195785378495</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>40.82390173576259</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>294.2532299697699</v>
       </c>
       <c r="U32" t="n">
-        <v>357.2135779556459</v>
+        <v>356.2178155722161</v>
       </c>
       <c r="V32" t="n">
         <v>337.8510241668239</v>
@@ -3093,7 +3093,7 @@
         <v>300.2818334606677</v>
       </c>
       <c r="Y32" t="n">
-        <v>214.4408702993763</v>
+        <v>219.3174326828064</v>
       </c>
     </row>
     <row r="33">
@@ -3218,19 +3218,19 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>272.5622555995538</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>342.3283181773756</v>
       </c>
       <c r="P34" t="n">
-        <v>135.6475972198461</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>430.215266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>432.6561607680363</v>
+        <v>68.3224289844627</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3267,7 +3267,7 @@
         <v>157.4745782429939</v>
       </c>
       <c r="D35" t="n">
-        <v>113.4625933564196</v>
+        <v>118.3391557398498</v>
       </c>
       <c r="E35" t="n">
         <v>112.3632896068686</v>
@@ -3288,7 +3288,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>76.6758595897859</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>200.6495748374988</v>
+        <v>199.6538124540693</v>
       </c>
       <c r="T35" t="n">
         <v>294.2532299697699</v>
@@ -3355,10 +3355,10 @@
         <v>47.63624233787687</v>
       </c>
       <c r="G36" t="n">
-        <v>33.68791323351792</v>
+        <v>33.68791323351791</v>
       </c>
       <c r="H36" t="n">
-        <v>39.66952114868531</v>
+        <v>39.66952114868528</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>33.4886037011847</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -3461,7 +3461,7 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>33.48860370118459</v>
       </c>
       <c r="Q37" t="n">
         <v>430.215266425598</v>
@@ -3525,10 +3525,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>35.85195785378495</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>40.82390173582978</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -3558,7 +3558,7 @@
         <v>357.2135779556459</v>
       </c>
       <c r="V38" t="n">
-        <v>332.974461783394</v>
+        <v>336.855261783394</v>
       </c>
       <c r="W38" t="n">
         <v>346.3734759809475</v>
@@ -3689,19 +3689,19 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>143.1095836489016</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>103.1078538958434</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>390.2135366725398</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>430.215266425598</v>
       </c>
       <c r="R40" t="n">
         <v>432.6561607680363</v>
@@ -3735,28 +3735,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>350.9993129555745</v>
+        <v>310.5405131175929</v>
       </c>
       <c r="C41" t="n">
-        <v>216.4949741934087</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>273.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>273.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>272.6608898749559</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>276.0215582010148</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>15.36152149172983</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3783,13 +3783,13 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>113.8179355117115</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>455.2532299697699</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>518.2135779556459</v>
@@ -3798,13 +3798,13 @@
         <v>498.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>507.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>461.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>380.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>253.5565566463266</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -3823,19 +3823,19 @@
         <v>216.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>211.6720972219126</v>
       </c>
       <c r="F42" t="n">
-        <v>208.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>194.6879132335179</v>
       </c>
       <c r="H42" t="n">
-        <v>200.6695211486853</v>
+        <v>187.9943626758749</v>
       </c>
       <c r="I42" t="n">
-        <v>84.3490274007825</v>
+        <v>84.34902740078249</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3868,19 +3868,19 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>188.7013505406146</v>
+        <v>274.1496897458157</v>
       </c>
       <c r="U42" t="n">
-        <v>269.2069635337717</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>283.5106671915202</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>288.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>268.3913927661343</v>
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>96.8249164393694</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>445.9993129555745</v>
       </c>
       <c r="C44" t="n">
         <v>413.4745782429939</v>
@@ -4020,25 +4020,25 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>208.8179355117115</v>
       </c>
       <c r="S44" t="n">
-        <v>377.0097149455769</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>366.0159331653944</v>
       </c>
       <c r="U44" t="n">
         <v>613.2135779556459</v>
       </c>
       <c r="V44" t="n">
-        <v>593.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>602.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>556.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -4051,13 +4051,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>348.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>118.5320722631633</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>311.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>306.6720972219126</v>
@@ -4069,10 +4069,10 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>295.6695211486853</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>179.3490274007825</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4105,19 +4105,19 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>190.7785580994971</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>378.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>383.8627394453875</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>3.715416439369418</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>772.7299014934888</v>
+        <v>1172.770305533893</v>
       </c>
       <c r="C2" t="n">
-        <v>722.7555800359191</v>
+        <v>1122.795984076323</v>
       </c>
       <c r="D2" t="n">
-        <v>712.3119883795052</v>
+        <v>1112.352392419909</v>
       </c>
       <c r="E2" t="n">
-        <v>707.904625140244</v>
+        <v>1036.050099268396</v>
       </c>
       <c r="F2" t="n">
-        <v>702.9656062432623</v>
+        <v>1031.111080371415</v>
       </c>
       <c r="G2" t="n">
-        <v>623.4528077704492</v>
+        <v>623.3728077704492</v>
       </c>
       <c r="H2" t="n">
-        <v>212.3199206987171</v>
+        <v>212.239920698717</v>
       </c>
       <c r="I2" t="n">
-        <v>64.48</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>463.8960489170527</v>
+        <v>458.0197404976271</v>
       </c>
       <c r="K2" t="n">
-        <v>1185.752610641806</v>
+        <v>1178.35160125138</v>
       </c>
       <c r="L2" t="n">
-        <v>1199.695445091583</v>
+        <v>1960.684720920271</v>
       </c>
       <c r="M2" t="n">
-        <v>1727.316326483835</v>
+        <v>1960.684720920271</v>
       </c>
       <c r="N2" t="n">
-        <v>2357.580088268649</v>
+        <v>1960.684720920271</v>
       </c>
       <c r="O2" t="n">
-        <v>2761.634720920271</v>
+        <v>2757.634720920271</v>
       </c>
       <c r="P2" t="n">
-        <v>2775.08608002271</v>
+        <v>2771.08608002271</v>
       </c>
       <c r="Q2" t="n">
-        <v>3224</v>
+        <v>3220</v>
       </c>
       <c r="R2" t="n">
-        <v>2976.709156048776</v>
+        <v>2972.709156048776</v>
       </c>
       <c r="S2" t="n">
-        <v>2479.083322879585</v>
+        <v>2879.12372691999</v>
       </c>
       <c r="T2" t="n">
-        <v>1886.908343112141</v>
+        <v>2690.989151192949</v>
       </c>
       <c r="U2" t="n">
-        <v>1635.177456288257</v>
+        <v>2439.258264369064</v>
       </c>
       <c r="V2" t="n">
-        <v>1403.004704604596</v>
+        <v>2207.085512685404</v>
       </c>
       <c r="W2" t="n">
-        <v>1162.223415734952</v>
+        <v>1966.30422381576</v>
       </c>
       <c r="X2" t="n">
-        <v>967.9993415322574</v>
+        <v>1772.080149613065</v>
       </c>
       <c r="Y2" t="n">
-        <v>855.5574903375035</v>
+        <v>1255.597894377907</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>839.4551138350674</v>
+        <v>281.9242701018005</v>
       </c>
       <c r="C3" t="n">
-        <v>839.4551138350674</v>
+        <v>281.9242701018005</v>
       </c>
       <c r="D3" t="n">
-        <v>839.4551138350674</v>
+        <v>281.9242701018005</v>
       </c>
       <c r="E3" t="n">
-        <v>839.4551138350674</v>
+        <v>281.9242701018005</v>
       </c>
       <c r="F3" t="n">
-        <v>496.3882023826665</v>
+        <v>281.9242701018005</v>
       </c>
       <c r="G3" t="n">
-        <v>496.3882023826665</v>
+        <v>281.9242701018005</v>
       </c>
       <c r="H3" t="n">
-        <v>282.0042701018006</v>
+        <v>281.9242701018005</v>
       </c>
       <c r="I3" t="n">
-        <v>64.48</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>193.2649556469971</v>
+        <v>193.1849556469971</v>
       </c>
       <c r="K3" t="n">
-        <v>390.7103370243993</v>
+        <v>390.6303370243993</v>
       </c>
       <c r="L3" t="n">
-        <v>673.1573910724296</v>
+        <v>673.0773910724296</v>
       </c>
       <c r="M3" t="n">
-        <v>772.1871328152888</v>
+        <v>772.1071328152888</v>
       </c>
       <c r="N3" t="n">
-        <v>918.75934421531</v>
+        <v>918.6793442153099</v>
       </c>
       <c r="O3" t="n">
-        <v>1169.961312125444</v>
+        <v>1169.881312125444</v>
       </c>
       <c r="P3" t="n">
-        <v>1292.249740368536</v>
+        <v>1292.169740368535</v>
       </c>
       <c r="Q3" t="n">
-        <v>1124.078346242456</v>
+        <v>1123.998346242455</v>
       </c>
       <c r="R3" t="n">
-        <v>978.554441982953</v>
+        <v>825.06400229009</v>
       </c>
       <c r="S3" t="n">
-        <v>912.286631841455</v>
+        <v>354.7557881081879</v>
       </c>
       <c r="T3" t="n">
-        <v>907.0849250274997</v>
+        <v>349.5540812942327</v>
       </c>
       <c r="U3" t="n">
-        <v>906.8758709529828</v>
+        <v>349.3450272197159</v>
       </c>
       <c r="V3" t="n">
-        <v>892.2186313655887</v>
+        <v>334.6877876323218</v>
       </c>
       <c r="W3" t="n">
-        <v>859.5184870122266</v>
+        <v>301.9876432789596</v>
       </c>
       <c r="X3" t="n">
-        <v>839.4551138350674</v>
+        <v>281.9242701018005</v>
       </c>
       <c r="Y3" t="n">
-        <v>839.4551138350674</v>
+        <v>281.9242701018005</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>556.824931308594</v>
+        <v>836.7440379477471</v>
       </c>
       <c r="C4" t="n">
-        <v>682.8269371270299</v>
+        <v>962.7460437661829</v>
       </c>
       <c r="D4" t="n">
-        <v>682.8269371270299</v>
+        <v>1076.065187891183</v>
       </c>
       <c r="E4" t="n">
-        <v>682.8269371270299</v>
+        <v>1193.894092102596</v>
       </c>
       <c r="F4" t="n">
-        <v>682.8269371270299</v>
+        <v>1318.255064694531</v>
       </c>
       <c r="G4" t="n">
-        <v>836.2763489155544</v>
+        <v>1471.704476483056</v>
       </c>
       <c r="H4" t="n">
-        <v>836.2763489155544</v>
+        <v>1471.704476483056</v>
       </c>
       <c r="I4" t="n">
-        <v>1058.697720966391</v>
+        <v>1538.073015555711</v>
       </c>
       <c r="J4" t="n">
-        <v>1422.810666864744</v>
+        <v>1538.073015555711</v>
       </c>
       <c r="K4" t="n">
-        <v>1538.153015555711</v>
+        <v>1538.073015555711</v>
       </c>
       <c r="L4" t="n">
-        <v>1520.86688676577</v>
+        <v>1520.78688676577</v>
       </c>
       <c r="M4" t="n">
-        <v>1405.869431962731</v>
+        <v>1405.789431962731</v>
       </c>
       <c r="N4" t="n">
-        <v>1239.644931357121</v>
+        <v>1239.564931357121</v>
       </c>
       <c r="O4" t="n">
-        <v>1002.949660470883</v>
+        <v>1002.869660470883</v>
       </c>
       <c r="P4" t="n">
-        <v>717.8854820137722</v>
+        <v>717.805482013772</v>
       </c>
       <c r="Q4" t="n">
-        <v>392.4155159273095</v>
+        <v>392.3355159273094</v>
       </c>
       <c r="R4" t="n">
-        <v>64.48</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>102.4769423072879</v>
+        <v>102.3969423072879</v>
       </c>
       <c r="T4" t="n">
-        <v>161.7673747035923</v>
+        <v>290.6556903185518</v>
       </c>
       <c r="U4" t="n">
-        <v>161.7673747035923</v>
+        <v>290.6556903185518</v>
       </c>
       <c r="V4" t="n">
-        <v>161.7673747035923</v>
+        <v>290.6556903185518</v>
       </c>
       <c r="W4" t="n">
-        <v>333.6582929632697</v>
+        <v>462.5466085782292</v>
       </c>
       <c r="X4" t="n">
-        <v>333.6582929632697</v>
+        <v>613.5773996024227</v>
       </c>
       <c r="Y4" t="n">
-        <v>445.0675936423019</v>
+        <v>724.986700281455</v>
       </c>
     </row>
     <row r="5">
@@ -4534,76 +4534,76 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>696.9149715812373</v>
+        <v>1504.915779662045</v>
       </c>
       <c r="C5" t="n">
-        <v>242.9002460832636</v>
+        <v>1050.901054164072</v>
       </c>
       <c r="D5" t="n">
-        <v>232.4566544268496</v>
+        <v>636.4170584672537</v>
       </c>
       <c r="E5" t="n">
-        <v>228.0492911875884</v>
+        <v>227.9692911875884</v>
       </c>
       <c r="F5" t="n">
-        <v>223.1102722906067</v>
+        <v>223.0302722906067</v>
       </c>
       <c r="G5" t="n">
-        <v>219.4124037300452</v>
+        <v>219.3324037300452</v>
       </c>
       <c r="H5" t="n">
-        <v>212.3199206987171</v>
+        <v>212.239920698717</v>
       </c>
       <c r="I5" t="n">
-        <v>64.48</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>463.8960489170527</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>476.0462442939371</v>
+        <v>786.2565617247528</v>
       </c>
       <c r="L5" t="n">
-        <v>819.2614368456444</v>
+        <v>1583.206561724753</v>
       </c>
       <c r="M5" t="n">
-        <v>1346.882318237896</v>
+        <v>1583.206561724753</v>
       </c>
       <c r="N5" t="n">
-        <v>1977.14608002271</v>
+        <v>1200.69976227673</v>
       </c>
       <c r="O5" t="n">
-        <v>1977.14608002271</v>
+        <v>1997.64976227673</v>
       </c>
       <c r="P5" t="n">
-        <v>2775.08608002271</v>
+        <v>2794.59976227673</v>
       </c>
       <c r="Q5" t="n">
-        <v>3224</v>
+        <v>3220</v>
       </c>
       <c r="R5" t="n">
-        <v>2976.709156048776</v>
+        <v>2972.709156048776</v>
       </c>
       <c r="S5" t="n">
-        <v>2883.12372691999</v>
+        <v>2879.12372691999</v>
       </c>
       <c r="T5" t="n">
-        <v>2694.989151192949</v>
+        <v>2690.989151192949</v>
       </c>
       <c r="U5" t="n">
-        <v>2443.258264369064</v>
+        <v>2439.258264369064</v>
       </c>
       <c r="V5" t="n">
-        <v>1807.045108645</v>
+        <v>2135.190582773153</v>
       </c>
       <c r="W5" t="n">
-        <v>1490.448889863105</v>
+        <v>1894.409293903509</v>
       </c>
       <c r="X5" t="n">
-        <v>1296.22481566041</v>
+        <v>1700.185219700814</v>
       </c>
       <c r="Y5" t="n">
-        <v>1183.782964465656</v>
+        <v>1587.74336850606</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64.48</v>
+        <v>628.057701639086</v>
       </c>
       <c r="C6" t="n">
-        <v>64.48</v>
+        <v>628.057701639086</v>
       </c>
       <c r="D6" t="n">
-        <v>64.48</v>
+        <v>628.057701639086</v>
       </c>
       <c r="E6" t="n">
-        <v>64.48</v>
+        <v>281.9242701018005</v>
       </c>
       <c r="F6" t="n">
-        <v>64.48</v>
+        <v>281.9242701018005</v>
       </c>
       <c r="G6" t="n">
-        <v>64.48</v>
+        <v>281.9242701018005</v>
       </c>
       <c r="H6" t="n">
-        <v>64.48</v>
+        <v>281.9242701018005</v>
       </c>
       <c r="I6" t="n">
-        <v>64.48</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>193.2649556469971</v>
+        <v>193.1849556469971</v>
       </c>
       <c r="K6" t="n">
-        <v>390.7103370243993</v>
+        <v>390.6303370243993</v>
       </c>
       <c r="L6" t="n">
-        <v>673.1573910724296</v>
+        <v>673.0773910724296</v>
       </c>
       <c r="M6" t="n">
-        <v>772.1871328152888</v>
+        <v>772.1071328152888</v>
       </c>
       <c r="N6" t="n">
-        <v>918.75934421531</v>
+        <v>918.6793442153099</v>
       </c>
       <c r="O6" t="n">
-        <v>1169.961312125444</v>
+        <v>1169.881312125444</v>
       </c>
       <c r="P6" t="n">
-        <v>1292.249740368536</v>
+        <v>1292.169740368535</v>
       </c>
       <c r="Q6" t="n">
-        <v>1124.078346242456</v>
+        <v>1292.169740368535</v>
       </c>
       <c r="R6" t="n">
-        <v>607.6197321882895</v>
+        <v>1146.645836109033</v>
       </c>
       <c r="S6" t="n">
-        <v>137.3115180063874</v>
+        <v>1080.378025967535</v>
       </c>
       <c r="T6" t="n">
-        <v>132.1098111924322</v>
+        <v>1075.17631915358</v>
       </c>
       <c r="U6" t="n">
-        <v>131.9007571179154</v>
+        <v>1074.967265079063</v>
       </c>
       <c r="V6" t="n">
-        <v>117.2435175305213</v>
+        <v>1060.310025491669</v>
       </c>
       <c r="W6" t="n">
-        <v>84.54337317715914</v>
+        <v>1027.609881138306</v>
       </c>
       <c r="X6" t="n">
-        <v>64.48</v>
+        <v>628.057701639086</v>
       </c>
       <c r="Y6" t="n">
-        <v>64.48</v>
+        <v>628.057701639086</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>822.2139869826018</v>
+        <v>723.1479013642727</v>
       </c>
       <c r="C7" t="n">
-        <v>948.2159928010376</v>
+        <v>849.1499071827085</v>
       </c>
       <c r="D7" t="n">
-        <v>1061.535136926038</v>
+        <v>962.4690513077086</v>
       </c>
       <c r="E7" t="n">
-        <v>1179.364041137451</v>
+        <v>962.4690513077086</v>
       </c>
       <c r="F7" t="n">
-        <v>1303.725013729386</v>
+        <v>962.4690513077086</v>
       </c>
       <c r="G7" t="n">
-        <v>1303.725013729386</v>
+        <v>1115.918463096233</v>
       </c>
       <c r="H7" t="n">
-        <v>1303.725013729386</v>
+        <v>1115.918463096233</v>
       </c>
       <c r="I7" t="n">
-        <v>1303.725013729386</v>
+        <v>1338.33983514707</v>
       </c>
       <c r="J7" t="n">
-        <v>1538.153015555711</v>
+        <v>1538.073015555711</v>
       </c>
       <c r="K7" t="n">
-        <v>1538.153015555711</v>
+        <v>1538.073015555711</v>
       </c>
       <c r="L7" t="n">
-        <v>1520.86688676577</v>
+        <v>1520.78688676577</v>
       </c>
       <c r="M7" t="n">
-        <v>1405.869431962731</v>
+        <v>1405.789431962731</v>
       </c>
       <c r="N7" t="n">
-        <v>1239.644931357121</v>
+        <v>1239.564931357121</v>
       </c>
       <c r="O7" t="n">
-        <v>1002.949660470883</v>
+        <v>1002.869660470883</v>
       </c>
       <c r="P7" t="n">
-        <v>717.8854820137722</v>
+        <v>717.805482013772</v>
       </c>
       <c r="Q7" t="n">
-        <v>392.4155159273095</v>
+        <v>392.3355159273094</v>
       </c>
       <c r="R7" t="n">
-        <v>64.48</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="S7" t="n">
-        <v>64.48</v>
+        <v>102.3969423072879</v>
       </c>
       <c r="T7" t="n">
-        <v>252.7387480112639</v>
+        <v>102.3969423072879</v>
       </c>
       <c r="U7" t="n">
-        <v>499.2922776987309</v>
+        <v>348.9504719947548</v>
       </c>
       <c r="V7" t="n">
-        <v>499.2922776987309</v>
+        <v>348.9504719947548</v>
       </c>
       <c r="W7" t="n">
-        <v>671.1831959584083</v>
+        <v>348.9504719947548</v>
       </c>
       <c r="X7" t="n">
-        <v>822.2139869826018</v>
+        <v>499.9812630189483</v>
       </c>
       <c r="Y7" t="n">
-        <v>822.2139869826018</v>
+        <v>611.3905636979806</v>
       </c>
     </row>
     <row r="8">
@@ -4771,76 +4771,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1020.020745444713</v>
+        <v>144.9546468421161</v>
       </c>
       <c r="C8" t="n">
-        <v>646.9406501236676</v>
+        <v>94.98032538454652</v>
       </c>
       <c r="D8" t="n">
-        <v>636.4970584672537</v>
+        <v>84.53673372813259</v>
       </c>
       <c r="E8" t="n">
-        <v>632.0896952279925</v>
+        <v>80.12937048887133</v>
       </c>
       <c r="F8" t="n">
-        <v>627.1506763310108</v>
+        <v>75.19035159188965</v>
       </c>
       <c r="G8" t="n">
-        <v>219.4124037300452</v>
+        <v>71.49248303132813</v>
       </c>
       <c r="H8" t="n">
-        <v>212.3199206987171</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>64.48</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>463.8960489170527</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>1185.752610641806</v>
+        <v>784.7318607537525</v>
       </c>
       <c r="L8" t="n">
-        <v>1852.60816329135</v>
+        <v>1275.793200551969</v>
       </c>
       <c r="M8" t="n">
-        <v>1795.796238215186</v>
+        <v>1803.41408194422</v>
       </c>
       <c r="N8" t="n">
-        <v>2426.06</v>
+        <v>2433.677843729034</v>
       </c>
       <c r="O8" t="n">
-        <v>2426.06</v>
+        <v>2433.677843729034</v>
       </c>
       <c r="P8" t="n">
-        <v>3224</v>
+        <v>2771.08608002271</v>
       </c>
       <c r="Q8" t="n">
-        <v>3224</v>
+        <v>3220</v>
       </c>
       <c r="R8" t="n">
-        <v>3224</v>
+        <v>2972.709156048776</v>
       </c>
       <c r="S8" t="n">
-        <v>3130.414570871214</v>
+        <v>2475.083322879585</v>
       </c>
       <c r="T8" t="n">
-        <v>2538.239591103769</v>
+        <v>2286.948747152545</v>
       </c>
       <c r="U8" t="n">
-        <v>2286.508704279885</v>
+        <v>1815.483009717692</v>
       </c>
       <c r="V8" t="n">
-        <v>2054.335952596224</v>
+        <v>1179.269853993628</v>
       </c>
       <c r="W8" t="n">
-        <v>1813.55466372658</v>
+        <v>938.4885651239836</v>
       </c>
       <c r="X8" t="n">
-        <v>1619.330589523885</v>
+        <v>744.2644909212888</v>
       </c>
       <c r="Y8" t="n">
-        <v>1102.848334288728</v>
+        <v>227.7822356861308</v>
       </c>
     </row>
     <row r="9">
@@ -4850,76 +4850,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>603.5861039207435</v>
+        <v>603.5061039207433</v>
       </c>
       <c r="C9" t="n">
-        <v>603.5861039207435</v>
+        <v>603.5061039207433</v>
       </c>
       <c r="D9" t="n">
-        <v>603.5861039207435</v>
+        <v>603.5061039207433</v>
       </c>
       <c r="E9" t="n">
-        <v>407.5469114524009</v>
+        <v>603.5061039207433</v>
       </c>
       <c r="F9" t="n">
-        <v>64.48</v>
+        <v>603.5061039207433</v>
       </c>
       <c r="G9" t="n">
-        <v>64.48</v>
+        <v>603.5061039207433</v>
       </c>
       <c r="H9" t="n">
-        <v>64.48</v>
+        <v>268.4863855887379</v>
       </c>
       <c r="I9" t="n">
-        <v>64.48</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>193.2649556469971</v>
+        <v>193.1849556469971</v>
       </c>
       <c r="K9" t="n">
-        <v>390.7103370243993</v>
+        <v>390.6303370243993</v>
       </c>
       <c r="L9" t="n">
-        <v>673.1573910724296</v>
+        <v>673.0773910724296</v>
       </c>
       <c r="M9" t="n">
-        <v>772.1871328152888</v>
+        <v>772.1071328152888</v>
       </c>
       <c r="N9" t="n">
-        <v>918.75934421531</v>
+        <v>918.6793442153099</v>
       </c>
       <c r="O9" t="n">
-        <v>1169.961312125444</v>
+        <v>1169.881312125444</v>
       </c>
       <c r="P9" t="n">
-        <v>1292.249740368536</v>
+        <v>1292.169740368535</v>
       </c>
       <c r="Q9" t="n">
-        <v>1292.249740368536</v>
+        <v>1292.169740368535</v>
       </c>
       <c r="R9" t="n">
-        <v>1146.725836109033</v>
+        <v>742.6054320686288</v>
       </c>
       <c r="S9" t="n">
-        <v>1080.458025967535</v>
+        <v>676.3376219271308</v>
       </c>
       <c r="T9" t="n">
-        <v>1075.25631915358</v>
+        <v>671.1359151131755</v>
       </c>
       <c r="U9" t="n">
-        <v>1075.047265079063</v>
+        <v>670.9268610386587</v>
       </c>
       <c r="V9" t="n">
-        <v>1060.390025491669</v>
+        <v>656.2696214512646</v>
       </c>
       <c r="W9" t="n">
-        <v>623.6494770979027</v>
+        <v>623.5694770979024</v>
       </c>
       <c r="X9" t="n">
-        <v>603.5861039207435</v>
+        <v>603.5061039207433</v>
       </c>
       <c r="Y9" t="n">
-        <v>603.5861039207435</v>
+        <v>603.5061039207433</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>583.4268149847368</v>
+        <v>698.0336705846769</v>
       </c>
       <c r="C10" t="n">
-        <v>709.4288208031726</v>
+        <v>698.0336705846769</v>
       </c>
       <c r="D10" t="n">
-        <v>709.4288208031726</v>
+        <v>698.0336705846769</v>
       </c>
       <c r="E10" t="n">
-        <v>827.2577250145856</v>
+        <v>815.8625747960899</v>
       </c>
       <c r="F10" t="n">
-        <v>951.6186976065211</v>
+        <v>940.2235473880254</v>
       </c>
       <c r="G10" t="n">
-        <v>951.6186976065211</v>
+        <v>1093.67295917655</v>
       </c>
       <c r="H10" t="n">
-        <v>951.6186976065211</v>
+        <v>1200.309294813907</v>
       </c>
       <c r="I10" t="n">
-        <v>1174.040069657358</v>
+        <v>1422.730666864744</v>
       </c>
       <c r="J10" t="n">
-        <v>1538.153015555711</v>
+        <v>1422.730666864744</v>
       </c>
       <c r="K10" t="n">
-        <v>1538.153015555711</v>
+        <v>1538.073015555711</v>
       </c>
       <c r="L10" t="n">
-        <v>1520.86688676577</v>
+        <v>1520.78688676577</v>
       </c>
       <c r="M10" t="n">
-        <v>1405.869431962731</v>
+        <v>1405.789431962731</v>
       </c>
       <c r="N10" t="n">
-        <v>1239.644931357121</v>
+        <v>1239.564931357121</v>
       </c>
       <c r="O10" t="n">
-        <v>1002.949660470883</v>
+        <v>1002.869660470883</v>
       </c>
       <c r="P10" t="n">
-        <v>717.8854820137722</v>
+        <v>717.805482013772</v>
       </c>
       <c r="Q10" t="n">
-        <v>392.4155159273095</v>
+        <v>392.3355159273094</v>
       </c>
       <c r="R10" t="n">
-        <v>64.48</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>102.4769423072879</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>290.7356903185517</v>
+        <v>252.6587480112639</v>
       </c>
       <c r="U10" t="n">
-        <v>320.6386862942511</v>
+        <v>499.2122776987309</v>
       </c>
       <c r="V10" t="n">
-        <v>320.6386862942511</v>
+        <v>698.0336705846769</v>
       </c>
       <c r="W10" t="n">
-        <v>320.6386862942511</v>
+        <v>698.0336705846769</v>
       </c>
       <c r="X10" t="n">
-        <v>471.6694773184446</v>
+        <v>698.0336705846769</v>
       </c>
       <c r="Y10" t="n">
-        <v>471.6694773184446</v>
+        <v>698.0336705846769</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>814.5947800563082</v>
+        <v>860.0817382746166</v>
       </c>
       <c r="C11" t="n">
-        <v>814.5947800563082</v>
+        <v>629.2993360089662</v>
       </c>
       <c r="D11" t="n">
-        <v>623.3431075918135</v>
+        <v>438.0476635444714</v>
       </c>
       <c r="E11" t="n">
-        <v>438.1276635444714</v>
+        <v>438.0476635444714</v>
       </c>
       <c r="F11" t="n">
-        <v>252.3805638394089</v>
+        <v>252.3005638394089</v>
       </c>
       <c r="G11" t="n">
-        <v>252.3805638394089</v>
+        <v>252.3005638394089</v>
       </c>
       <c r="H11" t="n">
-        <v>64.48</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>64.48</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>463.8960489170527</v>
+        <v>463.8160489170527</v>
       </c>
       <c r="K11" t="n">
-        <v>1185.752610641806</v>
+        <v>649.5651986304582</v>
       </c>
       <c r="L11" t="n">
-        <v>1983.692610641805</v>
+        <v>1446.515198630458</v>
       </c>
       <c r="M11" t="n">
-        <v>1983.692610641806</v>
+        <v>1974.13608002271</v>
       </c>
       <c r="N11" t="n">
-        <v>2613.956372426619</v>
+        <v>1974.13608002271</v>
       </c>
       <c r="O11" t="n">
-        <v>2761.634720920271</v>
+        <v>1974.13608002271</v>
       </c>
       <c r="P11" t="n">
-        <v>2775.08608002271</v>
+        <v>2771.08608002271</v>
       </c>
       <c r="Q11" t="n">
-        <v>3224</v>
+        <v>3220</v>
       </c>
       <c r="R11" t="n">
-        <v>3199.941479281099</v>
+        <v>3195.941479281099</v>
       </c>
       <c r="S11" t="n">
-        <v>2925.547969344232</v>
+        <v>2921.547969344232</v>
       </c>
       <c r="T11" t="n">
-        <v>2556.605312809111</v>
+        <v>2921.547969344232</v>
       </c>
       <c r="U11" t="n">
-        <v>2124.066345177145</v>
+        <v>2489.009001712267</v>
       </c>
       <c r="V11" t="n">
-        <v>1711.085512685404</v>
+        <v>2076.028169220525</v>
       </c>
       <c r="W11" t="n">
-        <v>1289.496143007679</v>
+        <v>1654.438799542801</v>
       </c>
       <c r="X11" t="n">
-        <v>1078.230449708404</v>
+        <v>1279.406644532025</v>
       </c>
       <c r="Y11" t="n">
-        <v>1078.230449708404</v>
+        <v>986.1567125291903</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>794.4834073588027</v>
+        <v>794.4034073588026</v>
       </c>
       <c r="C12" t="n">
-        <v>652.9683442825205</v>
+        <v>652.8883442825205</v>
       </c>
       <c r="D12" t="n">
-        <v>524.7484585272654</v>
+        <v>524.6684585272653</v>
       </c>
       <c r="E12" t="n">
-        <v>401.8473502223031</v>
+        <v>401.7673502223031</v>
       </c>
       <c r="F12" t="n">
-        <v>282.0127620022255</v>
+        <v>281.9327620022254</v>
       </c>
       <c r="G12" t="n">
-        <v>176.2673950996821</v>
+        <v>176.1873950996821</v>
       </c>
       <c r="H12" t="n">
-        <v>64.48</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>64.48</v>
+        <v>69.99446287322533</v>
       </c>
       <c r="J12" t="n">
-        <v>412.0549556469971</v>
+        <v>278.3603898047134</v>
       </c>
       <c r="K12" t="n">
-        <v>640.7105545650875</v>
+        <v>694.5957711821156</v>
       </c>
       <c r="L12" t="n">
-        <v>1141.947608613118</v>
+        <v>1195.832825230146</v>
       </c>
       <c r="M12" t="n">
-        <v>1459.767350355977</v>
+        <v>1513.652566973005</v>
       </c>
       <c r="N12" t="n">
-        <v>1825.129561755998</v>
+        <v>1879.014778373026</v>
       </c>
       <c r="O12" t="n">
-        <v>2295.121529666132</v>
+        <v>2349.00674628316</v>
       </c>
       <c r="P12" t="n">
-        <v>2636.199957909223</v>
+        <v>2690.085174526252</v>
       </c>
       <c r="Q12" t="n">
-        <v>2690.165174526252</v>
+        <v>2690.085174526252</v>
       </c>
       <c r="R12" t="n">
-        <v>2363.833189458669</v>
+        <v>2363.753189458669</v>
       </c>
       <c r="S12" t="n">
-        <v>2116.75729850909</v>
+        <v>2116.67729850909</v>
       </c>
       <c r="T12" t="n">
-        <v>1930.747510887054</v>
+        <v>1930.667510887054</v>
       </c>
       <c r="U12" t="n">
-        <v>1749.730376004457</v>
+        <v>1749.650376004456</v>
       </c>
       <c r="V12" t="n">
-        <v>1554.265055608982</v>
+        <v>1554.185055608981</v>
       </c>
       <c r="W12" t="n">
-        <v>1340.756830447539</v>
+        <v>1340.676830447538</v>
       </c>
       <c r="X12" t="n">
-        <v>1139.885376462299</v>
+        <v>1139.805376462298</v>
       </c>
       <c r="Y12" t="n">
-        <v>959.6920504359002</v>
+        <v>959.6120504359002</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>161.0565899395155</v>
+        <v>166.4036705846768</v>
       </c>
       <c r="C13" t="n">
-        <v>161.0565899395155</v>
+        <v>166.4036705846768</v>
       </c>
       <c r="D13" t="n">
-        <v>161.0565899395155</v>
+        <v>166.4036705846768</v>
       </c>
       <c r="E13" t="n">
-        <v>161.0565899395155</v>
+        <v>166.4036705846768</v>
       </c>
       <c r="F13" t="n">
-        <v>161.0565899395155</v>
+        <v>166.4036705846768</v>
       </c>
       <c r="G13" t="n">
-        <v>161.0565899395155</v>
+        <v>166.4036705846768</v>
       </c>
       <c r="H13" t="n">
-        <v>153.5956412361087</v>
+        <v>166.4036705846768</v>
       </c>
       <c r="I13" t="n">
-        <v>198.8070132869457</v>
+        <v>211.6150426355138</v>
       </c>
       <c r="J13" t="n">
-        <v>385.7099591852987</v>
+        <v>398.5179885338668</v>
       </c>
       <c r="K13" t="n">
-        <v>385.7099591852987</v>
+        <v>398.5179885338668</v>
       </c>
       <c r="L13" t="n">
-        <v>385.7099591852987</v>
+        <v>398.5179885338668</v>
       </c>
       <c r="M13" t="n">
-        <v>385.7099591852987</v>
+        <v>398.5179885338668</v>
       </c>
       <c r="N13" t="n">
-        <v>385.7099591852987</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>385.7099591852987</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>385.7099591852987</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>385.7099591852987</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="R13" t="n">
-        <v>64.48</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>64.48</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>75.52874801126389</v>
+        <v>75.44874801126389</v>
       </c>
       <c r="U13" t="n">
-        <v>144.8722776987308</v>
+        <v>144.7922776987309</v>
       </c>
       <c r="V13" t="n">
-        <v>166.4836705846768</v>
+        <v>166.4036705846768</v>
       </c>
       <c r="W13" t="n">
-        <v>161.0565899395155</v>
+        <v>166.4036705846768</v>
       </c>
       <c r="X13" t="n">
-        <v>161.0565899395155</v>
+        <v>166.4036705846768</v>
       </c>
       <c r="Y13" t="n">
-        <v>161.0565899395155</v>
+        <v>166.4036705846768</v>
       </c>
     </row>
     <row r="14">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>926.3660317686192</v>
+        <v>1084.428586236056</v>
       </c>
       <c r="C14" t="n">
-        <v>719.826053745393</v>
+        <v>877.8886082128295</v>
       </c>
       <c r="D14" t="n">
-        <v>552.8168055233225</v>
+        <v>710.879359990759</v>
       </c>
       <c r="E14" t="n">
-        <v>391.8437857184047</v>
+        <v>549.9063401858411</v>
       </c>
       <c r="F14" t="n">
-        <v>230.3391102557664</v>
+        <v>388.4016647232028</v>
       </c>
       <c r="G14" t="n">
-        <v>70.0755851295483</v>
+        <v>228.1381395969847</v>
       </c>
       <c r="H14" t="n">
         <v>64.48</v>
@@ -5281,7 +5281,7 @@
         <v>1728.446883792851</v>
       </c>
       <c r="N14" t="n">
-        <v>1963.694720920271</v>
+        <v>2358.710645577665</v>
       </c>
       <c r="O14" t="n">
         <v>2761.634720920271</v>
@@ -5296,25 +5296,25 @@
         <v>3224</v>
       </c>
       <c r="S14" t="n">
-        <v>2973.848914305557</v>
+        <v>3224</v>
       </c>
       <c r="T14" t="n">
-        <v>2629.14868201286</v>
+        <v>2879.299767707303</v>
       </c>
       <c r="U14" t="n">
-        <v>2220.852138623319</v>
+        <v>2471.003224317762</v>
       </c>
       <c r="V14" t="n">
-        <v>1832.113730374002</v>
+        <v>2340.966015609789</v>
       </c>
       <c r="W14" t="n">
-        <v>1434.766784938701</v>
+        <v>1943.619070174489</v>
       </c>
       <c r="X14" t="n">
-        <v>1434.766784938701</v>
+        <v>1592.829339406137</v>
       </c>
       <c r="Y14" t="n">
-        <v>1165.75927717829</v>
+        <v>1323.821831645727</v>
       </c>
     </row>
     <row r="15">
@@ -5345,28 +5345,28 @@
         <v>64.48</v>
       </c>
       <c r="I15" t="n">
-        <v>93.83446287322533</v>
+        <v>64.48</v>
       </c>
       <c r="J15" t="n">
-        <v>222.6194185202224</v>
+        <v>257.3440261683506</v>
       </c>
       <c r="K15" t="n">
-        <v>420.0647998976247</v>
+        <v>697.3394075457528</v>
       </c>
       <c r="L15" t="n">
-        <v>702.5118539456549</v>
+        <v>979.7864615937831</v>
       </c>
       <c r="M15" t="n">
-        <v>1044.091595688514</v>
+        <v>1321.366203336642</v>
       </c>
       <c r="N15" t="n">
-        <v>1390.213198119635</v>
+        <v>1710.488414736663</v>
       </c>
       <c r="O15" t="n">
-        <v>1883.965166029769</v>
+        <v>1961.690382646797</v>
       </c>
       <c r="P15" t="n">
-        <v>2248.80359427286</v>
+        <v>2326.528810889889</v>
       </c>
       <c r="Q15" t="n">
         <v>2326.528810889889</v>
@@ -5430,25 +5430,25 @@
         <v>552.2864309693352</v>
       </c>
       <c r="K16" t="n">
-        <v>513.4050399796064</v>
+        <v>552.2864309693352</v>
       </c>
       <c r="L16" t="n">
-        <v>513.4050399796064</v>
+        <v>552.2864309693352</v>
       </c>
       <c r="M16" t="n">
-        <v>513.4050399796064</v>
+        <v>552.2864309693352</v>
       </c>
       <c r="N16" t="n">
-        <v>513.4050399796064</v>
+        <v>552.2864309693352</v>
       </c>
       <c r="O16" t="n">
-        <v>120.1441125277118</v>
+        <v>552.2864309693352</v>
       </c>
       <c r="P16" t="n">
-        <v>64.48</v>
+        <v>552.2864309693352</v>
       </c>
       <c r="Q16" t="n">
-        <v>64.48</v>
+        <v>70.25080831721607</v>
       </c>
       <c r="R16" t="n">
         <v>64.48</v>
@@ -5497,7 +5497,7 @@
         <v>315.9130158510517</v>
       </c>
       <c r="G17" t="n">
-        <v>192.01312708847</v>
+        <v>191.7745032333484</v>
       </c>
       <c r="H17" t="n">
         <v>64.48</v>
@@ -5509,22 +5509,22 @@
         <v>463.8960489170527</v>
       </c>
       <c r="K17" t="n">
-        <v>1185.752610641806</v>
+        <v>476.0462442939371</v>
       </c>
       <c r="L17" t="n">
-        <v>1983.692610641805</v>
+        <v>491.1196360527311</v>
       </c>
       <c r="M17" t="n">
-        <v>2511.313492034057</v>
+        <v>1018.740517444983</v>
       </c>
       <c r="N17" t="n">
-        <v>2511.313492034057</v>
+        <v>1649.004279229796</v>
       </c>
       <c r="O17" t="n">
-        <v>3210.548640897561</v>
+        <v>2446.944279229796</v>
       </c>
       <c r="P17" t="n">
-        <v>3224</v>
+        <v>2775.08608002271</v>
       </c>
       <c r="Q17" t="n">
         <v>3224</v>
@@ -5561,19 +5561,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>430.8470437224389</v>
+        <v>430.847043722439</v>
       </c>
       <c r="C18" t="n">
-        <v>349.9380412522174</v>
+        <v>349.9380412522175</v>
       </c>
       <c r="D18" t="n">
-        <v>282.3242161030229</v>
+        <v>282.324216103023</v>
       </c>
       <c r="E18" t="n">
         <v>220.0291684041213</v>
       </c>
       <c r="F18" t="n">
-        <v>160.8006407901042</v>
+        <v>160.8006407901043</v>
       </c>
       <c r="G18" t="n">
         <v>115.6613344936215</v>
@@ -5591,16 +5591,16 @@
         <v>390.7103370243993</v>
       </c>
       <c r="L18" t="n">
-        <v>673.1573910724296</v>
+        <v>951.3473910724297</v>
       </c>
       <c r="M18" t="n">
-        <v>1050.377132815289</v>
+        <v>1261.011657882096</v>
       </c>
       <c r="N18" t="n">
-        <v>1196.94934421531</v>
+        <v>1407.583869282117</v>
       </c>
       <c r="O18" t="n">
-        <v>1448.151312125444</v>
+        <v>1658.785837192251</v>
       </c>
       <c r="P18" t="n">
         <v>1781.074265435343</v>
@@ -5615,22 +5615,22 @@
         <v>1328.878510630302</v>
       </c>
       <c r="T18" t="n">
-        <v>1203.474783614326</v>
+        <v>1203.474783614327</v>
       </c>
       <c r="U18" t="n">
         <v>1083.06370933779</v>
       </c>
       <c r="V18" t="n">
-        <v>948.2044495483754</v>
+        <v>948.2044495483755</v>
       </c>
       <c r="W18" t="n">
-        <v>795.302284992993</v>
+        <v>795.3022849929931</v>
       </c>
       <c r="X18" t="n">
-        <v>655.0368916138136</v>
+        <v>655.0368916138137</v>
       </c>
       <c r="Y18" t="n">
-        <v>535.4496261934759</v>
+        <v>535.449626193476</v>
       </c>
     </row>
     <row r="19">
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>431.9853798685477</v>
+        <v>431.9853798685478</v>
       </c>
       <c r="C19" t="n">
         <v>440.1773856869835</v>
@@ -5649,13 +5649,13 @@
         <v>440.1773856869835</v>
       </c>
       <c r="E19" t="n">
-        <v>440.1962898983965</v>
+        <v>440.1962898983966</v>
       </c>
       <c r="F19" t="n">
         <v>446.747262490332</v>
       </c>
       <c r="G19" t="n">
-        <v>482.3866742788566</v>
+        <v>482.3866742788567</v>
       </c>
       <c r="H19" t="n">
         <v>534.4741984546476</v>
@@ -5667,22 +5667,22 @@
         <v>885.3885164038376</v>
       </c>
       <c r="K19" t="n">
-        <v>882.8707617777451</v>
+        <v>885.3885164038376</v>
       </c>
       <c r="L19" t="n">
-        <v>882.8707617777451</v>
+        <v>747.9003674118765</v>
       </c>
       <c r="M19" t="n">
-        <v>647.6712867726856</v>
+        <v>747.9003674118765</v>
       </c>
       <c r="N19" t="n">
-        <v>421.3772910882582</v>
+        <v>510.1519862884829</v>
       </c>
       <c r="O19" t="n">
-        <v>64.48</v>
+        <v>510.1519862884829</v>
       </c>
       <c r="P19" t="n">
-        <v>64.48</v>
+        <v>510.1519862884829</v>
       </c>
       <c r="Q19" t="n">
         <v>64.48</v>
@@ -5700,16 +5700,16 @@
         <v>263.6722776987309</v>
       </c>
       <c r="V19" t="n">
-        <v>344.6836705846768</v>
+        <v>344.6836705846769</v>
       </c>
       <c r="W19" t="n">
-        <v>398.7645888443542</v>
+        <v>398.7645888443543</v>
       </c>
       <c r="X19" t="n">
-        <v>431.9853798685477</v>
+        <v>431.9853798685478</v>
       </c>
       <c r="Y19" t="n">
-        <v>431.9853798685477</v>
+        <v>431.9853798685478</v>
       </c>
     </row>
     <row r="20">
@@ -5719,49 +5719,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>866.2467680542375</v>
+        <v>866.4853919093589</v>
       </c>
       <c r="C20" t="n">
-        <v>696.0704263946476</v>
+        <v>696.3090502497691</v>
       </c>
       <c r="D20" t="n">
-        <v>565.4248145362135</v>
+        <v>565.663438391335</v>
       </c>
       <c r="E20" t="n">
-        <v>440.815431094932</v>
+        <v>441.0540549500536</v>
       </c>
       <c r="F20" t="n">
-        <v>315.6743919959301</v>
+        <v>315.9130158510517</v>
       </c>
       <c r="G20" t="n">
-        <v>191.7745032333484</v>
+        <v>192.01312708847</v>
       </c>
       <c r="H20" t="n">
-        <v>64.48</v>
+        <v>64.71862385512162</v>
       </c>
       <c r="I20" t="n">
         <v>64.48</v>
       </c>
       <c r="J20" t="n">
-        <v>64.48</v>
+        <v>463.8960489170527</v>
       </c>
       <c r="K20" t="n">
-        <v>786.3365617247528</v>
+        <v>476.0462442939371</v>
       </c>
       <c r="L20" t="n">
-        <v>1584.276561724753</v>
+        <v>1100.499118607748</v>
       </c>
       <c r="M20" t="n">
-        <v>2111.897443117005</v>
+        <v>1628.12</v>
       </c>
       <c r="N20" t="n">
-        <v>2742.161204901818</v>
+        <v>1628.12</v>
       </c>
       <c r="O20" t="n">
-        <v>2761.634720920271</v>
+        <v>2426.06</v>
       </c>
       <c r="P20" t="n">
-        <v>2775.08608002271</v>
+        <v>3224</v>
       </c>
       <c r="Q20" t="n">
         <v>3224</v>
@@ -5770,25 +5770,25 @@
         <v>3224</v>
       </c>
       <c r="S20" t="n">
-        <v>3009.973926814072</v>
+        <v>3010.212550669193</v>
       </c>
       <c r="T20" t="n">
-        <v>2701.637330885011</v>
+        <v>2701.875954740133</v>
       </c>
       <c r="U20" t="n">
-        <v>2329.704423859106</v>
+        <v>2329.943047714228</v>
       </c>
       <c r="V20" t="n">
-        <v>1977.329651973426</v>
+        <v>1977.568275828547</v>
       </c>
       <c r="W20" t="n">
-        <v>1616.346342901761</v>
+        <v>1616.584966756883</v>
       </c>
       <c r="X20" t="n">
-        <v>1301.920248497046</v>
+        <v>1302.158872352168</v>
       </c>
       <c r="Y20" t="n">
-        <v>1069.276377100272</v>
+        <v>1069.515000955394</v>
       </c>
     </row>
     <row r="21">
@@ -5825,19 +5825,19 @@
         <v>193.2649556469971</v>
       </c>
       <c r="K21" t="n">
-        <v>390.7103370243993</v>
+        <v>601.3448620912067</v>
       </c>
       <c r="L21" t="n">
-        <v>673.1573910724296</v>
+        <v>1161.981916139237</v>
       </c>
       <c r="M21" t="n">
-        <v>772.1871328152888</v>
+        <v>1261.011657882096</v>
       </c>
       <c r="N21" t="n">
-        <v>1129.393869282118</v>
+        <v>1407.583869282117</v>
       </c>
       <c r="O21" t="n">
-        <v>1380.595837192252</v>
+        <v>1658.785837192251</v>
       </c>
       <c r="P21" t="n">
         <v>1781.074265435343</v>
@@ -5877,55 +5877,55 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>419.2791645286074</v>
+        <v>425.8098239725088</v>
       </c>
       <c r="C22" t="n">
-        <v>427.4711703470431</v>
+        <v>434.0018297909445</v>
       </c>
       <c r="D22" t="n">
-        <v>427.4711703470431</v>
+        <v>434.0018297909445</v>
       </c>
       <c r="E22" t="n">
-        <v>427.4900745584562</v>
+        <v>434.0207340023575</v>
       </c>
       <c r="F22" t="n">
-        <v>434.0410471503916</v>
+        <v>440.571706594293</v>
       </c>
       <c r="G22" t="n">
-        <v>469.6804589389163</v>
+        <v>476.2111183828176</v>
       </c>
       <c r="H22" t="n">
-        <v>521.7679831147072</v>
+        <v>528.2986425586087</v>
       </c>
       <c r="I22" t="n">
-        <v>626.3793551655442</v>
+        <v>632.9100146094456</v>
       </c>
       <c r="J22" t="n">
-        <v>872.6823010638972</v>
+        <v>879.2129605077986</v>
       </c>
       <c r="K22" t="n">
-        <v>870.1645464378047</v>
+        <v>879.2129605077986</v>
       </c>
       <c r="L22" t="n">
-        <v>870.1645464378047</v>
+        <v>879.2129605077986</v>
       </c>
       <c r="M22" t="n">
-        <v>870.1645464378047</v>
+        <v>879.2129605077986</v>
       </c>
       <c r="N22" t="n">
-        <v>870.1645464378047</v>
+        <v>826.6434897473894</v>
       </c>
       <c r="O22" t="n">
-        <v>870.1645464378047</v>
+        <v>469.7461986591312</v>
       </c>
       <c r="P22" t="n">
-        <v>591.5855723436937</v>
+        <v>64.48</v>
       </c>
       <c r="Q22" t="n">
-        <v>145.9135860552108</v>
+        <v>64.48</v>
       </c>
       <c r="R22" t="n">
-        <v>145.9135860552108</v>
+        <v>64.48</v>
       </c>
       <c r="S22" t="n">
         <v>64.48</v>
@@ -5946,7 +5946,7 @@
         <v>431.9853798685478</v>
       </c>
       <c r="Y22" t="n">
-        <v>425.4547204246464</v>
+        <v>431.9853798685478</v>
       </c>
     </row>
     <row r="23">
@@ -5956,25 +5956,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>866.2467680542375</v>
+        <v>866.4853919093589</v>
       </c>
       <c r="C23" t="n">
-        <v>696.0704263946476</v>
+        <v>696.3090502497691</v>
       </c>
       <c r="D23" t="n">
-        <v>565.4248145362135</v>
+        <v>565.663438391335</v>
       </c>
       <c r="E23" t="n">
-        <v>440.815431094932</v>
+        <v>441.0540549500536</v>
       </c>
       <c r="F23" t="n">
-        <v>315.6743919959301</v>
+        <v>315.9130158510517</v>
       </c>
       <c r="G23" t="n">
-        <v>191.7745032333484</v>
+        <v>192.01312708847</v>
       </c>
       <c r="H23" t="n">
-        <v>64.48</v>
+        <v>64.71862385512162</v>
       </c>
       <c r="I23" t="n">
         <v>64.48</v>
@@ -5986,16 +5986,16 @@
         <v>786.3365617247528</v>
       </c>
       <c r="L23" t="n">
-        <v>1346.882318237896</v>
+        <v>1584.276561724753</v>
       </c>
       <c r="M23" t="n">
-        <v>1346.882318237896</v>
+        <v>1584.276561724753</v>
       </c>
       <c r="N23" t="n">
-        <v>1977.14608002271</v>
+        <v>2214.540323509566</v>
       </c>
       <c r="O23" t="n">
-        <v>1977.14608002271</v>
+        <v>2761.634720920271</v>
       </c>
       <c r="P23" t="n">
         <v>2775.08608002271</v>
@@ -6004,28 +6004,28 @@
         <v>3224</v>
       </c>
       <c r="R23" t="n">
-        <v>3223.761376144878</v>
+        <v>3224</v>
       </c>
       <c r="S23" t="n">
-        <v>3009.973926814072</v>
+        <v>3010.212550669193</v>
       </c>
       <c r="T23" t="n">
-        <v>2701.637330885011</v>
+        <v>2701.875954740133</v>
       </c>
       <c r="U23" t="n">
-        <v>2329.704423859106</v>
+        <v>2329.943047714228</v>
       </c>
       <c r="V23" t="n">
-        <v>1977.329651973426</v>
+        <v>1977.568275828547</v>
       </c>
       <c r="W23" t="n">
-        <v>1616.346342901761</v>
+        <v>1616.584966756883</v>
       </c>
       <c r="X23" t="n">
-        <v>1301.920248497046</v>
+        <v>1302.158872352168</v>
       </c>
       <c r="Y23" t="n">
-        <v>1069.276377100272</v>
+        <v>1069.515000955394</v>
       </c>
     </row>
     <row r="24">
@@ -6035,19 +6035,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>430.847043722439</v>
+        <v>430.8470437224389</v>
       </c>
       <c r="C24" t="n">
-        <v>349.9380412522175</v>
+        <v>349.9380412522174</v>
       </c>
       <c r="D24" t="n">
-        <v>282.324216103023</v>
+        <v>282.3242161030229</v>
       </c>
       <c r="E24" t="n">
         <v>220.0291684041213</v>
       </c>
       <c r="F24" t="n">
-        <v>160.8006407901043</v>
+        <v>160.8006407901042</v>
       </c>
       <c r="G24" t="n">
         <v>115.6613344936215</v>
@@ -6062,19 +6062,19 @@
         <v>193.2649556469971</v>
       </c>
       <c r="K24" t="n">
-        <v>668.9003370243993</v>
+        <v>601.3448620912069</v>
       </c>
       <c r="L24" t="n">
-        <v>1161.981916139237</v>
+        <v>883.7919161392372</v>
       </c>
       <c r="M24" t="n">
-        <v>1261.011657882096</v>
+        <v>982.8216578820964</v>
       </c>
       <c r="N24" t="n">
-        <v>1407.583869282117</v>
+        <v>1129.393869282118</v>
       </c>
       <c r="O24" t="n">
-        <v>1658.785837192251</v>
+        <v>1380.595837192252</v>
       </c>
       <c r="P24" t="n">
         <v>1781.074265435343</v>
@@ -6089,22 +6089,22 @@
         <v>1328.878510630302</v>
       </c>
       <c r="T24" t="n">
-        <v>1203.474783614327</v>
+        <v>1203.474783614326</v>
       </c>
       <c r="U24" t="n">
         <v>1083.06370933779</v>
       </c>
       <c r="V24" t="n">
-        <v>948.2044495483755</v>
+        <v>948.2044495483754</v>
       </c>
       <c r="W24" t="n">
-        <v>795.3022849929931</v>
+        <v>795.302284992993</v>
       </c>
       <c r="X24" t="n">
-        <v>655.0368916138137</v>
+        <v>655.0368916138136</v>
       </c>
       <c r="Y24" t="n">
-        <v>535.449626193476</v>
+        <v>535.4496261934759</v>
       </c>
     </row>
     <row r="25">
@@ -6114,52 +6114,52 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>425.4547204246464</v>
+        <v>425.8098239725087</v>
       </c>
       <c r="C25" t="n">
-        <v>433.6467262430822</v>
+        <v>434.0018297909444</v>
       </c>
       <c r="D25" t="n">
-        <v>433.6467262430822</v>
+        <v>429.4197913509894</v>
       </c>
       <c r="E25" t="n">
-        <v>433.6656304544952</v>
+        <v>429.4386955624024</v>
       </c>
       <c r="F25" t="n">
-        <v>440.2166030464307</v>
+        <v>435.9896681543379</v>
       </c>
       <c r="G25" t="n">
-        <v>475.8560148349553</v>
+        <v>471.6290799428625</v>
       </c>
       <c r="H25" t="n">
-        <v>527.9435390107463</v>
+        <v>523.7166041186535</v>
       </c>
       <c r="I25" t="n">
-        <v>632.5549110615833</v>
+        <v>628.3279761694905</v>
       </c>
       <c r="J25" t="n">
-        <v>878.8578569599363</v>
+        <v>874.6309220678435</v>
       </c>
       <c r="K25" t="n">
-        <v>878.8578569599363</v>
+        <v>874.6309220678435</v>
       </c>
       <c r="L25" t="n">
-        <v>878.8578569599363</v>
+        <v>737.1427730758824</v>
       </c>
       <c r="M25" t="n">
-        <v>878.8578569599363</v>
+        <v>501.9432980708228</v>
       </c>
       <c r="N25" t="n">
-        <v>592.4313361523061</v>
+        <v>215.5167772631927</v>
       </c>
       <c r="O25" t="n">
-        <v>235.5340450640479</v>
+        <v>215.5167772631927</v>
       </c>
       <c r="P25" t="n">
-        <v>235.5340450640479</v>
+        <v>215.5167772631927</v>
       </c>
       <c r="Q25" t="n">
-        <v>235.5340450640479</v>
+        <v>64.48</v>
       </c>
       <c r="R25" t="n">
         <v>64.48</v>
@@ -6174,16 +6174,16 @@
         <v>263.6722776987309</v>
       </c>
       <c r="V25" t="n">
-        <v>344.6836705846769</v>
+        <v>344.6836705846768</v>
       </c>
       <c r="W25" t="n">
-        <v>398.7645888443543</v>
+        <v>398.7645888443542</v>
       </c>
       <c r="X25" t="n">
-        <v>431.9853798685478</v>
+        <v>431.9853798685477</v>
       </c>
       <c r="Y25" t="n">
-        <v>425.4547204246464</v>
+        <v>431.9853798685477</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1038.702567851192</v>
+        <v>853.0354681461297</v>
       </c>
       <c r="C26" t="n">
-        <v>807.9201655855417</v>
+        <v>622.2530658804792</v>
       </c>
       <c r="D26" t="n">
-        <v>616.6684931210469</v>
+        <v>431.0013934159845</v>
       </c>
       <c r="E26" t="n">
-        <v>431.4530490737048</v>
+        <v>245.7859493686423</v>
       </c>
       <c r="F26" t="n">
-        <v>245.7059493686423</v>
+        <v>245.7859493686423</v>
       </c>
       <c r="G26" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="H26" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="I26" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="J26" t="n">
-        <v>460.6160489170527</v>
+        <v>61.28</v>
       </c>
       <c r="K26" t="n">
-        <v>1182.472610641805</v>
+        <v>73.43019537688443</v>
       </c>
       <c r="L26" t="n">
-        <v>1197.546002400599</v>
+        <v>685.4100777431796</v>
       </c>
       <c r="M26" t="n">
-        <v>1725.166883792851</v>
+        <v>1213.030959135431</v>
       </c>
       <c r="N26" t="n">
-        <v>1853.736080022686</v>
+        <v>1843.294720920245</v>
       </c>
       <c r="O26" t="n">
-        <v>1853.736080022686</v>
+        <v>2601.634720920271</v>
       </c>
       <c r="P26" t="n">
-        <v>2611.08608002271</v>
+        <v>2615.08608002271</v>
       </c>
       <c r="Q26" t="n">
-        <v>3060</v>
+        <v>3064</v>
       </c>
       <c r="R26" t="n">
-        <v>3035.941479281099</v>
+        <v>3064</v>
       </c>
       <c r="S26" t="n">
-        <v>3035.941479281099</v>
+        <v>2789.606490063133</v>
       </c>
       <c r="T26" t="n">
-        <v>2666.998822745978</v>
+        <v>2420.663833528011</v>
       </c>
       <c r="U26" t="n">
-        <v>2234.459855114012</v>
+        <v>2197.934057303577</v>
       </c>
       <c r="V26" t="n">
-        <v>1821.479022622271</v>
+        <v>1784.953224811835</v>
       </c>
       <c r="W26" t="n">
-        <v>1706.984654864802</v>
+        <v>1784.953224811835</v>
       </c>
       <c r="X26" t="n">
-        <v>1331.952499854027</v>
+        <v>1409.92106980106</v>
       </c>
       <c r="Y26" t="n">
-        <v>1038.702567851192</v>
+        <v>1116.671137798225</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>791.2034073588026</v>
+        <v>791.2834073588027</v>
       </c>
       <c r="C27" t="n">
-        <v>649.6883442825205</v>
+        <v>649.7683442825206</v>
       </c>
       <c r="D27" t="n">
-        <v>521.4684585272653</v>
+        <v>521.5484585272654</v>
       </c>
       <c r="E27" t="n">
-        <v>398.567350222303</v>
+        <v>398.6473502223031</v>
       </c>
       <c r="F27" t="n">
-        <v>278.7327620022254</v>
+        <v>278.8127620022255</v>
       </c>
       <c r="G27" t="n">
-        <v>172.9873950996821</v>
+        <v>173.0673950996821</v>
       </c>
       <c r="H27" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="I27" t="n">
-        <v>66.79446287322533</v>
+        <v>61.28</v>
       </c>
       <c r="J27" t="n">
-        <v>414.3694185202224</v>
+        <v>408.854955646997</v>
       </c>
       <c r="K27" t="n">
-        <v>830.6047998976246</v>
+        <v>825.0903370243993</v>
       </c>
       <c r="L27" t="n">
-        <v>1331.841853945655</v>
+        <v>1326.32739107243</v>
       </c>
       <c r="M27" t="n">
-        <v>1649.661595688514</v>
+        <v>1644.147132815289</v>
       </c>
       <c r="N27" t="n">
-        <v>1821.849561755997</v>
+        <v>1821.929561755997</v>
       </c>
       <c r="O27" t="n">
-        <v>2291.841529666131</v>
+        <v>2291.921529666131</v>
       </c>
       <c r="P27" t="n">
-        <v>2632.919957909223</v>
+        <v>2632.999957909223</v>
       </c>
       <c r="Q27" t="n">
-        <v>2686.885174526252</v>
+        <v>2686.965174526252</v>
       </c>
       <c r="R27" t="n">
-        <v>2360.553189458669</v>
+        <v>2360.633189458669</v>
       </c>
       <c r="S27" t="n">
-        <v>2113.47729850909</v>
+        <v>2113.55729850909</v>
       </c>
       <c r="T27" t="n">
-        <v>1927.467510887054</v>
+        <v>1927.547510887054</v>
       </c>
       <c r="U27" t="n">
-        <v>1746.450376004456</v>
+        <v>1746.530376004456</v>
       </c>
       <c r="V27" t="n">
-        <v>1550.985055608981</v>
+        <v>1551.065055608981</v>
       </c>
       <c r="W27" t="n">
-        <v>1337.476830447538</v>
+        <v>1337.556830447538</v>
       </c>
       <c r="X27" t="n">
-        <v>1136.605376462298</v>
+        <v>1136.685376462299</v>
       </c>
       <c r="Y27" t="n">
-        <v>956.4120504359001</v>
+        <v>956.4920504359003</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>129.2477212659892</v>
+        <v>113.5277238869138</v>
       </c>
       <c r="C28" t="n">
-        <v>129.2477212659892</v>
+        <v>61.28</v>
       </c>
       <c r="D28" t="n">
-        <v>129.2477212659892</v>
+        <v>61.28</v>
       </c>
       <c r="E28" t="n">
-        <v>68.66094870340679</v>
+        <v>61.28</v>
       </c>
       <c r="F28" t="n">
-        <v>68.66094870340679</v>
+        <v>61.28</v>
       </c>
       <c r="G28" t="n">
-        <v>68.66094870340679</v>
+        <v>61.28</v>
       </c>
       <c r="H28" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="I28" t="n">
-        <v>106.411372050837</v>
+        <v>106.491372050837</v>
       </c>
       <c r="J28" t="n">
-        <v>293.31431794919</v>
+        <v>293.3943179491899</v>
       </c>
       <c r="K28" t="n">
-        <v>293.31431794919</v>
+        <v>293.3943179491899</v>
       </c>
       <c r="L28" t="n">
-        <v>293.31431794919</v>
+        <v>293.3943179491899</v>
       </c>
       <c r="M28" t="n">
-        <v>293.31431794919</v>
+        <v>293.3943179491899</v>
       </c>
       <c r="N28" t="n">
-        <v>293.31431794919</v>
+        <v>61.28</v>
       </c>
       <c r="O28" t="n">
-        <v>94.02566718341197</v>
+        <v>61.28</v>
       </c>
       <c r="P28" t="n">
-        <v>94.02566718341197</v>
+        <v>61.28</v>
       </c>
       <c r="Q28" t="n">
-        <v>94.02566718341197</v>
+        <v>61.28</v>
       </c>
       <c r="R28" t="n">
-        <v>94.02566718341197</v>
+        <v>61.28</v>
       </c>
       <c r="S28" t="n">
-        <v>94.02566718341197</v>
+        <v>61.28</v>
       </c>
       <c r="T28" t="n">
-        <v>105.0744151946759</v>
+        <v>72.3287480112639</v>
       </c>
       <c r="U28" t="n">
-        <v>174.4179448821428</v>
+        <v>141.6722776987309</v>
       </c>
       <c r="V28" t="n">
-        <v>196.0293377680888</v>
+        <v>163.2836705846768</v>
       </c>
       <c r="W28" t="n">
-        <v>196.0293377680888</v>
+        <v>163.2836705846768</v>
       </c>
       <c r="X28" t="n">
-        <v>196.0293377680888</v>
+        <v>163.2836705846768</v>
       </c>
       <c r="Y28" t="n">
-        <v>196.0293377680888</v>
+        <v>113.5277238869138</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>791.3742807982475</v>
+        <v>796.3801013875707</v>
       </c>
       <c r="C29" t="n">
-        <v>632.3090502497687</v>
+        <v>637.314870839092</v>
       </c>
       <c r="D29" t="n">
-        <v>517.7003700917691</v>
+        <v>517.780370091769</v>
       </c>
       <c r="E29" t="n">
-        <v>404.2020977615987</v>
+        <v>404.2820977615986</v>
       </c>
       <c r="F29" t="n">
-        <v>290.1721697737079</v>
+        <v>290.2521697737078</v>
       </c>
       <c r="G29" t="n">
-        <v>177.3833921222372</v>
+        <v>177.4633921222372</v>
       </c>
       <c r="H29" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="I29" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="J29" t="n">
-        <v>409.3766655674822</v>
+        <v>61.28</v>
       </c>
       <c r="K29" t="n">
-        <v>1130.512566725275</v>
+        <v>783.1365617247528</v>
       </c>
       <c r="L29" t="n">
-        <v>1144.765356822917</v>
+        <v>1541.476561724753</v>
       </c>
       <c r="M29" t="n">
-        <v>1672.386238215169</v>
+        <v>1541.476561724753</v>
       </c>
       <c r="N29" t="n">
-        <v>2302.649999999982</v>
+        <v>2171.740323509566</v>
       </c>
       <c r="O29" t="n">
-        <v>2302.649999999982</v>
+        <v>2930.080323509587</v>
       </c>
       <c r="P29" t="n">
-        <v>3060</v>
+        <v>3064</v>
       </c>
       <c r="Q29" t="n">
-        <v>3060</v>
+        <v>3064</v>
       </c>
       <c r="R29" t="n">
-        <v>3060</v>
+        <v>3064</v>
       </c>
       <c r="S29" t="n">
-        <v>2857.323661780304</v>
+        <v>2861.323661780304</v>
       </c>
       <c r="T29" t="n">
-        <v>2560.098176962355</v>
+        <v>2564.098176962355</v>
       </c>
       <c r="U29" t="n">
-        <v>2199.276381047561</v>
+        <v>2203.276381047561</v>
       </c>
       <c r="V29" t="n">
-        <v>1858.012720272991</v>
+        <v>1862.012720272991</v>
       </c>
       <c r="W29" t="n">
-        <v>1508.140522312438</v>
+        <v>1513.146342901761</v>
       </c>
       <c r="X29" t="n">
-        <v>1204.825539018834</v>
+        <v>1209.831359608158</v>
       </c>
       <c r="Y29" t="n">
-        <v>983.2927787331712</v>
+        <v>988.2985993224944</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>360.9003770557724</v>
+        <v>360.9803770557724</v>
       </c>
       <c r="C30" t="n">
-        <v>291.102485696662</v>
+        <v>291.182485696662</v>
       </c>
       <c r="D30" t="n">
-        <v>234.5997716585785</v>
+        <v>234.6797716585785</v>
       </c>
       <c r="E30" t="n">
-        <v>183.415835070788</v>
+        <v>183.495835070788</v>
       </c>
       <c r="F30" t="n">
-        <v>135.298418567882</v>
+        <v>135.3784185678821</v>
       </c>
       <c r="G30" t="n">
-        <v>101.2702233825104</v>
+        <v>101.3502233825104</v>
       </c>
       <c r="H30" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="I30" t="n">
-        <v>137.0844628732253</v>
+        <v>137.1644628732253</v>
       </c>
       <c r="J30" t="n">
-        <v>265.8694185202224</v>
+        <v>265.9494185202224</v>
       </c>
       <c r="K30" t="n">
-        <v>463.3147998976247</v>
+        <v>463.3947998976246</v>
       </c>
       <c r="L30" t="n">
-        <v>745.7618539456549</v>
+        <v>745.8418539456549</v>
       </c>
       <c r="M30" t="n">
-        <v>844.7915956885141</v>
+        <v>1091.14499121543</v>
       </c>
       <c r="N30" t="n">
-        <v>1113.381985998422</v>
+        <v>1237.717202615451</v>
       </c>
       <c r="O30" t="n">
-        <v>1364.583953908556</v>
+        <v>1488.919170525585</v>
       </c>
       <c r="P30" t="n">
-        <v>1486.872382151648</v>
+        <v>1611.207598768677</v>
       </c>
       <c r="Q30" t="n">
-        <v>1611.127598768677</v>
+        <v>1611.207598768677</v>
       </c>
       <c r="R30" t="n">
-        <v>1356.512785418265</v>
+        <v>1356.592785418265</v>
       </c>
       <c r="S30" t="n">
-        <v>1181.154066185858</v>
+        <v>1181.234066185858</v>
       </c>
       <c r="T30" t="n">
-        <v>1066.861450280993</v>
+        <v>1066.941450280994</v>
       </c>
       <c r="U30" t="n">
-        <v>957.5614871155675</v>
+        <v>957.6414871155677</v>
       </c>
       <c r="V30" t="n">
-        <v>833.8133384372643</v>
+        <v>833.8933384372644</v>
       </c>
       <c r="W30" t="n">
-        <v>692.022284992993</v>
+        <v>692.1022849929932</v>
       </c>
       <c r="X30" t="n">
-        <v>562.8680027249248</v>
+        <v>562.9480027249249</v>
       </c>
       <c r="Y30" t="n">
-        <v>454.3918484156982</v>
+        <v>454.4718484156982</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>492.4820182138721</v>
+        <v>492.5620182138721</v>
       </c>
       <c r="C31" t="n">
-        <v>511.5640240323079</v>
+        <v>511.6440240323079</v>
       </c>
       <c r="D31" t="n">
-        <v>517.9631681573079</v>
+        <v>518.0431681573079</v>
       </c>
       <c r="E31" t="n">
-        <v>528.872072368721</v>
+        <v>528.952072368721</v>
       </c>
       <c r="F31" t="n">
-        <v>546.3130449606565</v>
+        <v>546.3930449606565</v>
       </c>
       <c r="G31" t="n">
-        <v>592.8424567491811</v>
+        <v>592.9224567491812</v>
       </c>
       <c r="H31" t="n">
-        <v>655.8199809249721</v>
+        <v>655.8999809249722</v>
       </c>
       <c r="I31" t="n">
-        <v>771.3213529758092</v>
+        <v>771.4013529758092</v>
       </c>
       <c r="J31" t="n">
-        <v>1028.514298874162</v>
+        <v>1028.594298874162</v>
       </c>
       <c r="K31" t="n">
-        <v>1036.936647565129</v>
+        <v>1037.016647565129</v>
       </c>
       <c r="L31" t="n">
-        <v>1036.936647565129</v>
+        <v>1037.016647565129</v>
       </c>
       <c r="M31" t="n">
-        <v>889.9159627253916</v>
+        <v>812.9282836711806</v>
       </c>
       <c r="N31" t="n">
-        <v>889.9159627253916</v>
+        <v>812.9282836711806</v>
       </c>
       <c r="O31" t="n">
-        <v>889.9159627253916</v>
+        <v>812.9282836711806</v>
       </c>
       <c r="P31" t="n">
-        <v>495.7608751773717</v>
+        <v>812.9282836711806</v>
       </c>
       <c r="Q31" t="n">
-        <v>61.2</v>
+        <v>498.3064250182185</v>
       </c>
       <c r="R31" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="S31" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="T31" t="n">
-        <v>142.5387480112639</v>
+        <v>142.6187480112639</v>
       </c>
       <c r="U31" t="n">
-        <v>282.1722776987308</v>
+        <v>282.2522776987308</v>
       </c>
       <c r="V31" t="n">
-        <v>374.0736705846767</v>
+        <v>374.1536705846768</v>
       </c>
       <c r="W31" t="n">
-        <v>439.0445888443542</v>
+        <v>439.1245888443542</v>
       </c>
       <c r="X31" t="n">
-        <v>483.1553798685477</v>
+        <v>483.2353798685477</v>
       </c>
       <c r="Y31" t="n">
-        <v>487.64468054758</v>
+        <v>487.72468054758</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>796.3001013875707</v>
+        <v>796.3801013875707</v>
       </c>
       <c r="C32" t="n">
-        <v>637.2348708390921</v>
+        <v>637.314870839092</v>
       </c>
       <c r="D32" t="n">
-        <v>517.7003700917691</v>
+        <v>517.780370091769</v>
       </c>
       <c r="E32" t="n">
-        <v>404.2020977615987</v>
+        <v>404.2820977615986</v>
       </c>
       <c r="F32" t="n">
-        <v>290.1721697737079</v>
+        <v>290.2521697737079</v>
       </c>
       <c r="G32" t="n">
-        <v>177.3833921222372</v>
+        <v>177.4633921222372</v>
       </c>
       <c r="H32" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="I32" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="J32" t="n">
-        <v>460.6160489170527</v>
+        <v>61.28</v>
       </c>
       <c r="K32" t="n">
-        <v>1181.751950074846</v>
+        <v>783.1365617247528</v>
       </c>
       <c r="L32" t="n">
-        <v>1196.004740172486</v>
+        <v>1541.476561724753</v>
       </c>
       <c r="M32" t="n">
-        <v>1723.625621564738</v>
+        <v>2069.097443117004</v>
       </c>
       <c r="N32" t="n">
-        <v>1723.625621564738</v>
+        <v>2699.361204901818</v>
       </c>
       <c r="O32" t="n">
-        <v>2480.975621564755</v>
+        <v>2699.361204901818</v>
       </c>
       <c r="P32" t="n">
-        <v>2611.08608002271</v>
+        <v>2712.812564004257</v>
       </c>
       <c r="Q32" t="n">
-        <v>3060</v>
+        <v>3064</v>
       </c>
       <c r="R32" t="n">
-        <v>3060</v>
+        <v>3064</v>
       </c>
       <c r="S32" t="n">
-        <v>2857.323661780304</v>
+        <v>2861.323661780304</v>
       </c>
       <c r="T32" t="n">
-        <v>2560.098176962355</v>
+        <v>2564.098176962355</v>
       </c>
       <c r="U32" t="n">
-        <v>2199.276381047561</v>
+        <v>2204.282201636884</v>
       </c>
       <c r="V32" t="n">
-        <v>1858.012720272991</v>
+        <v>1863.018540862314</v>
       </c>
       <c r="W32" t="n">
-        <v>1508.140522312438</v>
+        <v>1513.146342901761</v>
       </c>
       <c r="X32" t="n">
-        <v>1204.825539018834</v>
+        <v>1209.831359608158</v>
       </c>
       <c r="Y32" t="n">
-        <v>988.2185993224945</v>
+        <v>988.2985993224944</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>360.9003770557724</v>
+        <v>360.9803770557724</v>
       </c>
       <c r="C33" t="n">
-        <v>291.102485696662</v>
+        <v>291.182485696662</v>
       </c>
       <c r="D33" t="n">
-        <v>234.5997716585785</v>
+        <v>234.6797716585785</v>
       </c>
       <c r="E33" t="n">
-        <v>183.415835070788</v>
+        <v>183.495835070788</v>
       </c>
       <c r="F33" t="n">
-        <v>135.298418567882</v>
+        <v>135.378418567882</v>
       </c>
       <c r="G33" t="n">
-        <v>101.2702233825104</v>
+        <v>101.3502233825104</v>
       </c>
       <c r="H33" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="I33" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="J33" t="n">
-        <v>189.9849556469971</v>
+        <v>190.0649556469971</v>
       </c>
       <c r="K33" t="n">
-        <v>387.4303370243994</v>
+        <v>387.5103370243993</v>
       </c>
       <c r="L33" t="n">
-        <v>867.7800328555418</v>
+        <v>703.0352494725707</v>
       </c>
       <c r="M33" t="n">
-        <v>966.809774598401</v>
+        <v>802.0649912154299</v>
       </c>
       <c r="N33" t="n">
-        <v>1113.381985998422</v>
+        <v>948.6372026154511</v>
       </c>
       <c r="O33" t="n">
-        <v>1364.583953908556</v>
+        <v>1199.839170525585</v>
       </c>
       <c r="P33" t="n">
-        <v>1486.872382151648</v>
+        <v>1611.207598768677</v>
       </c>
       <c r="Q33" t="n">
-        <v>1611.127598768677</v>
+        <v>1611.207598768677</v>
       </c>
       <c r="R33" t="n">
-        <v>1356.512785418265</v>
+        <v>1356.592785418265</v>
       </c>
       <c r="S33" t="n">
-        <v>1181.154066185858</v>
+        <v>1181.234066185858</v>
       </c>
       <c r="T33" t="n">
-        <v>1066.861450280993</v>
+        <v>1066.941450280994</v>
       </c>
       <c r="U33" t="n">
-        <v>957.5614871155675</v>
+        <v>957.6414871155677</v>
       </c>
       <c r="V33" t="n">
-        <v>833.8133384372643</v>
+        <v>833.8933384372644</v>
       </c>
       <c r="W33" t="n">
-        <v>692.022284992993</v>
+        <v>692.1022849929932</v>
       </c>
       <c r="X33" t="n">
-        <v>562.8680027249248</v>
+        <v>562.9480027249249</v>
       </c>
       <c r="Y33" t="n">
-        <v>454.3918484156982</v>
+        <v>454.4718484156982</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>492.4820182138721</v>
+        <v>492.5620182138721</v>
       </c>
       <c r="C34" t="n">
-        <v>511.5640240323079</v>
+        <v>511.6440240323079</v>
       </c>
       <c r="D34" t="n">
-        <v>517.9631681573079</v>
+        <v>518.0431681573079</v>
       </c>
       <c r="E34" t="n">
-        <v>528.872072368721</v>
+        <v>528.952072368721</v>
       </c>
       <c r="F34" t="n">
-        <v>546.3130449606565</v>
+        <v>546.3930449606565</v>
       </c>
       <c r="G34" t="n">
-        <v>592.8424567491811</v>
+        <v>592.9224567491812</v>
       </c>
       <c r="H34" t="n">
-        <v>655.8199809249721</v>
+        <v>655.8999809249722</v>
       </c>
       <c r="I34" t="n">
-        <v>771.3213529758092</v>
+        <v>771.4013529758092</v>
       </c>
       <c r="J34" t="n">
-        <v>1028.514298874162</v>
+        <v>1028.594298874162</v>
       </c>
       <c r="K34" t="n">
-        <v>1036.936647565129</v>
+        <v>1037.016647565129</v>
       </c>
       <c r="L34" t="n">
-        <v>910.5596096842792</v>
+        <v>910.6396096842791</v>
       </c>
       <c r="M34" t="n">
-        <v>910.5596096842792</v>
+        <v>910.6396096842791</v>
       </c>
       <c r="N34" t="n">
-        <v>635.2441999877601</v>
+        <v>910.6396096842791</v>
       </c>
       <c r="O34" t="n">
-        <v>635.2441999877601</v>
+        <v>564.853429707132</v>
       </c>
       <c r="P34" t="n">
-        <v>498.2264250182185</v>
+        <v>564.853429707132</v>
       </c>
       <c r="Q34" t="n">
-        <v>498.2264250182185</v>
+        <v>130.2925545297603</v>
       </c>
       <c r="R34" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="S34" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="T34" t="n">
-        <v>142.5387480112639</v>
+        <v>142.6187480112639</v>
       </c>
       <c r="U34" t="n">
-        <v>282.1722776987308</v>
+        <v>282.2522776987308</v>
       </c>
       <c r="V34" t="n">
-        <v>374.0736705846767</v>
+        <v>374.1536705846768</v>
       </c>
       <c r="W34" t="n">
-        <v>439.0445888443542</v>
+        <v>439.1245888443542</v>
       </c>
       <c r="X34" t="n">
-        <v>483.1553798685477</v>
+        <v>483.2353798685477</v>
       </c>
       <c r="Y34" t="n">
-        <v>487.64468054758</v>
+        <v>487.72468054758</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>791.3742807982475</v>
+        <v>796.3801013875707</v>
       </c>
       <c r="C35" t="n">
-        <v>632.3090502497687</v>
+        <v>637.314870839092</v>
       </c>
       <c r="D35" t="n">
-        <v>517.7003700917691</v>
+        <v>517.780370091769</v>
       </c>
       <c r="E35" t="n">
-        <v>404.2020977615987</v>
+        <v>404.2820977615986</v>
       </c>
       <c r="F35" t="n">
-        <v>290.1721697737079</v>
+        <v>290.2521697737079</v>
       </c>
       <c r="G35" t="n">
-        <v>177.3833921222372</v>
+        <v>177.4633921222372</v>
       </c>
       <c r="H35" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="I35" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="J35" t="n">
-        <v>460.6160489170527</v>
+        <v>460.6960489170527</v>
       </c>
       <c r="K35" t="n">
-        <v>471.2249820658192</v>
+        <v>557.3338395279832</v>
       </c>
       <c r="L35" t="n">
-        <v>486.2983738246131</v>
+        <v>1315.673839527983</v>
       </c>
       <c r="M35" t="n">
-        <v>486.2983738246131</v>
+        <v>1843.294720920235</v>
       </c>
       <c r="N35" t="n">
-        <v>1116.562135609427</v>
+        <v>1843.294720920235</v>
       </c>
       <c r="O35" t="n">
-        <v>1873.912135609444</v>
+        <v>2601.634720920271</v>
       </c>
       <c r="P35" t="n">
-        <v>2611.08608002271</v>
+        <v>2615.08608002271</v>
       </c>
       <c r="Q35" t="n">
-        <v>3060</v>
+        <v>3064</v>
       </c>
       <c r="R35" t="n">
-        <v>3060</v>
+        <v>3064</v>
       </c>
       <c r="S35" t="n">
-        <v>2857.323661780304</v>
+        <v>2862.329482369627</v>
       </c>
       <c r="T35" t="n">
-        <v>2560.098176962355</v>
+        <v>2565.103997551677</v>
       </c>
       <c r="U35" t="n">
-        <v>2199.276381047561</v>
+        <v>2204.282201636884</v>
       </c>
       <c r="V35" t="n">
-        <v>1858.012720272991</v>
+        <v>1863.018540862314</v>
       </c>
       <c r="W35" t="n">
-        <v>1508.140522312438</v>
+        <v>1513.146342901761</v>
       </c>
       <c r="X35" t="n">
-        <v>1204.825539018834</v>
+        <v>1209.831359608158</v>
       </c>
       <c r="Y35" t="n">
-        <v>983.2927787331712</v>
+        <v>988.2985993224944</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>360.9003770557724</v>
+        <v>360.9803770557724</v>
       </c>
       <c r="C36" t="n">
-        <v>291.102485696662</v>
+        <v>291.182485696662</v>
       </c>
       <c r="D36" t="n">
-        <v>234.5997716585785</v>
+        <v>234.6797716585785</v>
       </c>
       <c r="E36" t="n">
-        <v>183.415835070788</v>
+        <v>183.495835070788</v>
       </c>
       <c r="F36" t="n">
-        <v>135.298418567882</v>
+        <v>135.378418567882</v>
       </c>
       <c r="G36" t="n">
-        <v>101.2702233825104</v>
+        <v>101.3502233825104</v>
       </c>
       <c r="H36" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="I36" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="J36" t="n">
-        <v>479.0649556469971</v>
+        <v>479.1449556469971</v>
       </c>
       <c r="K36" t="n">
-        <v>676.5103370243993</v>
+        <v>676.5903370243993</v>
       </c>
       <c r="L36" t="n">
-        <v>992.0352494725705</v>
+        <v>959.0373910724296</v>
       </c>
       <c r="M36" t="n">
-        <v>1091.06499121543</v>
+        <v>1058.067132815289</v>
       </c>
       <c r="N36" t="n">
-        <v>1237.637202615451</v>
+        <v>1204.63934421531</v>
       </c>
       <c r="O36" t="n">
-        <v>1488.839170525585</v>
+        <v>1455.841312125444</v>
       </c>
       <c r="P36" t="n">
-        <v>1611.127598768677</v>
+        <v>1611.207598768677</v>
       </c>
       <c r="Q36" t="n">
-        <v>1611.127598768677</v>
+        <v>1611.207598768677</v>
       </c>
       <c r="R36" t="n">
-        <v>1356.512785418265</v>
+        <v>1356.592785418265</v>
       </c>
       <c r="S36" t="n">
-        <v>1181.154066185858</v>
+        <v>1181.234066185858</v>
       </c>
       <c r="T36" t="n">
-        <v>1066.861450280993</v>
+        <v>1066.941450280994</v>
       </c>
       <c r="U36" t="n">
-        <v>957.5614871155675</v>
+        <v>957.6414871155677</v>
       </c>
       <c r="V36" t="n">
-        <v>833.8133384372643</v>
+        <v>833.8933384372644</v>
       </c>
       <c r="W36" t="n">
-        <v>692.022284992993</v>
+        <v>692.1022849929932</v>
       </c>
       <c r="X36" t="n">
-        <v>562.8680027249248</v>
+        <v>562.9480027249249</v>
       </c>
       <c r="Y36" t="n">
-        <v>454.3918484156982</v>
+        <v>454.4718484156982</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>492.4820182138722</v>
+        <v>492.5620182138721</v>
       </c>
       <c r="C37" t="n">
-        <v>511.564024032308</v>
+        <v>511.6440240323079</v>
       </c>
       <c r="D37" t="n">
-        <v>517.963168157308</v>
+        <v>518.0431681573079</v>
       </c>
       <c r="E37" t="n">
-        <v>528.8720723687211</v>
+        <v>528.952072368721</v>
       </c>
       <c r="F37" t="n">
-        <v>546.3130449606566</v>
+        <v>546.3930449606565</v>
       </c>
       <c r="G37" t="n">
-        <v>592.8424567491812</v>
+        <v>592.9224567491812</v>
       </c>
       <c r="H37" t="n">
-        <v>655.8199809249722</v>
+        <v>655.8999809249722</v>
       </c>
       <c r="I37" t="n">
-        <v>771.3213529758093</v>
+        <v>771.4013529758092</v>
       </c>
       <c r="J37" t="n">
-        <v>1028.514298874162</v>
+        <v>1028.594298874162</v>
       </c>
       <c r="K37" t="n">
-        <v>1036.936647565129</v>
+        <v>1037.016647565129</v>
       </c>
       <c r="L37" t="n">
-        <v>1003.10977513969</v>
+        <v>1037.016647565129</v>
       </c>
       <c r="M37" t="n">
-        <v>1003.10977513969</v>
+        <v>1037.016647565129</v>
       </c>
       <c r="N37" t="n">
-        <v>1003.10977513969</v>
+        <v>1037.016647565129</v>
       </c>
       <c r="O37" t="n">
-        <v>1003.10977513969</v>
+        <v>1037.016647565129</v>
       </c>
       <c r="P37" t="n">
-        <v>1003.10977513969</v>
+        <v>1003.18977513969</v>
       </c>
       <c r="Q37" t="n">
-        <v>568.5488999623183</v>
+        <v>568.6288999623183</v>
       </c>
       <c r="R37" t="n">
-        <v>131.5224749440997</v>
+        <v>131.6024749440997</v>
       </c>
       <c r="S37" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="T37" t="n">
-        <v>142.5387480112639</v>
+        <v>142.6187480112639</v>
       </c>
       <c r="U37" t="n">
-        <v>282.1722776987309</v>
+        <v>282.2522776987308</v>
       </c>
       <c r="V37" t="n">
-        <v>374.0736705846768</v>
+        <v>374.1536705846768</v>
       </c>
       <c r="W37" t="n">
-        <v>439.0445888443543</v>
+        <v>439.1245888443542</v>
       </c>
       <c r="X37" t="n">
-        <v>483.1553798685478</v>
+        <v>483.2353798685477</v>
       </c>
       <c r="Y37" t="n">
-        <v>487.6446805475801</v>
+        <v>487.72468054758</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>796.3001013875707</v>
+        <v>796.3801013875707</v>
       </c>
       <c r="C38" t="n">
-        <v>637.2348708390921</v>
+        <v>637.314870839092</v>
       </c>
       <c r="D38" t="n">
-        <v>517.7003700917691</v>
+        <v>517.780370091769</v>
       </c>
       <c r="E38" t="n">
-        <v>404.2020977615987</v>
+        <v>404.2820977615986</v>
       </c>
       <c r="F38" t="n">
-        <v>290.1721697737079</v>
+        <v>290.2521697737079</v>
       </c>
       <c r="G38" t="n">
-        <v>177.3833921222372</v>
+        <v>177.4633921222372</v>
       </c>
       <c r="H38" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="I38" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="J38" t="n">
-        <v>61.2</v>
+        <v>460.6960489170527</v>
       </c>
       <c r="K38" t="n">
-        <v>782.3359011577929</v>
+        <v>1182.552610641806</v>
       </c>
       <c r="L38" t="n">
-        <v>796.5886912554324</v>
+        <v>1197.6260024006</v>
       </c>
       <c r="M38" t="n">
-        <v>796.5886912554324</v>
+        <v>1725.246883792851</v>
       </c>
       <c r="N38" t="n">
-        <v>1096.386080022675</v>
+        <v>2355.510645577665</v>
       </c>
       <c r="O38" t="n">
-        <v>1853.736080022692</v>
+        <v>2601.634720920271</v>
       </c>
       <c r="P38" t="n">
-        <v>2611.08608002271</v>
+        <v>2615.08608002271</v>
       </c>
       <c r="Q38" t="n">
-        <v>3060</v>
+        <v>3064</v>
       </c>
       <c r="R38" t="n">
-        <v>3060</v>
+        <v>3064</v>
       </c>
       <c r="S38" t="n">
-        <v>2857.323661780304</v>
+        <v>2861.323661780304</v>
       </c>
       <c r="T38" t="n">
-        <v>2560.098176962355</v>
+        <v>2564.098176962355</v>
       </c>
       <c r="U38" t="n">
-        <v>2199.276381047561</v>
+        <v>2203.276381047561</v>
       </c>
       <c r="V38" t="n">
-        <v>1862.938540862314</v>
+        <v>1863.018540862314</v>
       </c>
       <c r="W38" t="n">
-        <v>1513.066342901761</v>
+        <v>1513.146342901761</v>
       </c>
       <c r="X38" t="n">
-        <v>1209.751359608158</v>
+        <v>1209.831359608158</v>
       </c>
       <c r="Y38" t="n">
-        <v>988.2185993224945</v>
+        <v>988.2985993224944</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>360.9003770557724</v>
+        <v>360.9803770557724</v>
       </c>
       <c r="C39" t="n">
-        <v>291.102485696662</v>
+        <v>291.182485696662</v>
       </c>
       <c r="D39" t="n">
-        <v>234.5997716585785</v>
+        <v>234.6797716585785</v>
       </c>
       <c r="E39" t="n">
-        <v>183.415835070788</v>
+        <v>183.495835070788</v>
       </c>
       <c r="F39" t="n">
-        <v>135.298418567882</v>
+        <v>135.378418567882</v>
       </c>
       <c r="G39" t="n">
-        <v>101.2702233825104</v>
+        <v>101.3502233825104</v>
       </c>
       <c r="H39" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="I39" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="J39" t="n">
-        <v>189.9849556469971</v>
+        <v>190.0649556469971</v>
       </c>
       <c r="K39" t="n">
-        <v>420.5081954245405</v>
+        <v>387.5103370243993</v>
       </c>
       <c r="L39" t="n">
-        <v>702.9552494725708</v>
+        <v>703.0352494725706</v>
       </c>
       <c r="M39" t="n">
-        <v>801.98499121543</v>
+        <v>802.0649912154298</v>
       </c>
       <c r="N39" t="n">
-        <v>948.5572026154512</v>
+        <v>948.637202615451</v>
       </c>
       <c r="O39" t="n">
-        <v>1199.759170525585</v>
+        <v>1488.919170525585</v>
       </c>
       <c r="P39" t="n">
-        <v>1611.127598768677</v>
+        <v>1611.207598768677</v>
       </c>
       <c r="Q39" t="n">
-        <v>1611.127598768677</v>
+        <v>1611.207598768677</v>
       </c>
       <c r="R39" t="n">
-        <v>1356.512785418265</v>
+        <v>1356.592785418265</v>
       </c>
       <c r="S39" t="n">
-        <v>1181.154066185858</v>
+        <v>1181.234066185858</v>
       </c>
       <c r="T39" t="n">
-        <v>1066.861450280993</v>
+        <v>1066.941450280994</v>
       </c>
       <c r="U39" t="n">
-        <v>957.5614871155675</v>
+        <v>957.6414871155677</v>
       </c>
       <c r="V39" t="n">
-        <v>833.8133384372643</v>
+        <v>833.8933384372644</v>
       </c>
       <c r="W39" t="n">
-        <v>692.022284992993</v>
+        <v>692.1022849929932</v>
       </c>
       <c r="X39" t="n">
-        <v>562.8680027249248</v>
+        <v>562.9480027249249</v>
       </c>
       <c r="Y39" t="n">
-        <v>454.3918484156982</v>
+        <v>454.4718484156982</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>492.4820182138721</v>
+        <v>492.5620182138721</v>
       </c>
       <c r="C40" t="n">
-        <v>511.5640240323079</v>
+        <v>511.6440240323079</v>
       </c>
       <c r="D40" t="n">
-        <v>517.9631681573079</v>
+        <v>518.0431681573079</v>
       </c>
       <c r="E40" t="n">
-        <v>528.872072368721</v>
+        <v>528.952072368721</v>
       </c>
       <c r="F40" t="n">
-        <v>546.3130449606565</v>
+        <v>546.3930449606565</v>
       </c>
       <c r="G40" t="n">
-        <v>592.8424567491811</v>
+        <v>592.9224567491812</v>
       </c>
       <c r="H40" t="n">
-        <v>655.8199809249721</v>
+        <v>655.8999809249722</v>
       </c>
       <c r="I40" t="n">
-        <v>771.3213529758092</v>
+        <v>771.4013529758092</v>
       </c>
       <c r="J40" t="n">
-        <v>1028.514298874162</v>
+        <v>1028.594298874162</v>
       </c>
       <c r="K40" t="n">
-        <v>1036.936647565129</v>
+        <v>1037.016647565129</v>
       </c>
       <c r="L40" t="n">
-        <v>1036.936647565129</v>
+        <v>1037.016647565129</v>
       </c>
       <c r="M40" t="n">
-        <v>892.3815125662386</v>
+        <v>1037.016647565129</v>
       </c>
       <c r="N40" t="n">
-        <v>892.3815125662386</v>
+        <v>932.8673001955902</v>
       </c>
       <c r="O40" t="n">
-        <v>892.3815125662386</v>
+        <v>932.8673001955902</v>
       </c>
       <c r="P40" t="n">
-        <v>498.2264250182185</v>
+        <v>932.8673001955902</v>
       </c>
       <c r="Q40" t="n">
-        <v>498.2264250182185</v>
+        <v>498.3064250182185</v>
       </c>
       <c r="R40" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="S40" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="T40" t="n">
-        <v>142.5387480112639</v>
+        <v>142.6187480112639</v>
       </c>
       <c r="U40" t="n">
-        <v>282.1722776987308</v>
+        <v>282.2522776987308</v>
       </c>
       <c r="V40" t="n">
-        <v>374.0736705846767</v>
+        <v>374.1536705846768</v>
       </c>
       <c r="W40" t="n">
-        <v>439.0445888443542</v>
+        <v>439.1245888443542</v>
       </c>
       <c r="X40" t="n">
-        <v>483.1553798685477</v>
+        <v>483.2353798685477</v>
       </c>
       <c r="Y40" t="n">
-        <v>487.64468054758</v>
+        <v>487.72468054758</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>834.1064871407873</v>
+        <v>629.577413946071</v>
       </c>
       <c r="C41" t="n">
-        <v>615.4246950262331</v>
+        <v>629.577413946071</v>
       </c>
       <c r="D41" t="n">
-        <v>615.4246950262331</v>
+        <v>629.577413946071</v>
       </c>
       <c r="E41" t="n">
-        <v>615.4246950262331</v>
+        <v>353.4528789896381</v>
       </c>
       <c r="F41" t="n">
-        <v>615.4246950262331</v>
+        <v>76.79668837548468</v>
       </c>
       <c r="G41" t="n">
-        <v>340.0096547484998</v>
+        <v>76.79668837548468</v>
       </c>
       <c r="H41" t="n">
-        <v>61.2</v>
+        <v>76.79668837548468</v>
       </c>
       <c r="I41" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="J41" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="K41" t="n">
-        <v>73.35019537688441</v>
+        <v>73.43019537688443</v>
       </c>
       <c r="L41" t="n">
-        <v>830.7001953768844</v>
+        <v>831.7701953768843</v>
       </c>
       <c r="M41" t="n">
-        <v>1210.02095913544</v>
+        <v>1098.406080022531</v>
       </c>
       <c r="N41" t="n">
-        <v>1840.284720920253</v>
+        <v>1098.406080022531</v>
       </c>
       <c r="O41" t="n">
-        <v>2597.634720920271</v>
+        <v>1856.74608002262</v>
       </c>
       <c r="P41" t="n">
-        <v>2611.08608002271</v>
+        <v>2615.08608002271</v>
       </c>
       <c r="Q41" t="n">
-        <v>3060</v>
+        <v>3064</v>
       </c>
       <c r="R41" t="n">
-        <v>3060</v>
+        <v>2949.032388372008</v>
       </c>
       <c r="S41" t="n">
-        <v>3060</v>
+        <v>2949.032388372008</v>
       </c>
       <c r="T41" t="n">
-        <v>2600.148252555788</v>
+        <v>2949.032388372008</v>
       </c>
       <c r="U41" t="n">
-        <v>2076.700194014732</v>
+        <v>2425.584329830952</v>
       </c>
       <c r="V41" t="n">
-        <v>1572.810270613899</v>
+        <v>1921.69440643012</v>
       </c>
       <c r="W41" t="n">
-        <v>1572.810270613899</v>
+        <v>1409.195945843304</v>
       </c>
       <c r="X41" t="n">
-        <v>1572.810270613899</v>
+        <v>943.2546999234376</v>
       </c>
       <c r="Y41" t="n">
-        <v>1188.651247701974</v>
+        <v>943.2546999234376</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>975.6246373924901</v>
+        <v>965.9679671007987</v>
       </c>
       <c r="C42" t="n">
-        <v>975.6246373924901</v>
+        <v>965.9679671007987</v>
       </c>
       <c r="D42" t="n">
-        <v>756.495660728144</v>
+        <v>746.8389904364526</v>
       </c>
       <c r="E42" t="n">
-        <v>756.495660728144</v>
+        <v>533.0287912223994</v>
       </c>
       <c r="F42" t="n">
-        <v>545.7519815989755</v>
+        <v>533.0287912223994</v>
       </c>
       <c r="G42" t="n">
-        <v>349.0975237873412</v>
+        <v>336.3743334107651</v>
       </c>
       <c r="H42" t="n">
-        <v>146.4010377785682</v>
+        <v>146.4810377785682</v>
       </c>
       <c r="I42" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="J42" t="n">
-        <v>319.674955646997</v>
+        <v>190.0649556469971</v>
       </c>
       <c r="K42" t="n">
-        <v>646.8103370243994</v>
+        <v>517.2003370243993</v>
       </c>
       <c r="L42" t="n">
-        <v>992.878900506392</v>
+        <v>929.3373910724297</v>
       </c>
       <c r="M42" t="n">
-        <v>1221.598642249251</v>
+        <v>1158.057132815289</v>
       </c>
       <c r="N42" t="n">
-        <v>1497.860853649272</v>
+        <v>1434.31934421531</v>
       </c>
       <c r="O42" t="n">
-        <v>1878.752821559407</v>
+        <v>1815.211312125444</v>
       </c>
       <c r="P42" t="n">
-        <v>2001.041249802498</v>
+        <v>2056.481407858169</v>
       </c>
       <c r="Q42" t="n">
-        <v>2001.041249802498</v>
+        <v>2056.481407858169</v>
       </c>
       <c r="R42" t="n">
-        <v>2001.041249802498</v>
+        <v>2056.481407858169</v>
       </c>
       <c r="S42" t="n">
-        <v>2001.041249802498</v>
+        <v>2056.481407858169</v>
       </c>
       <c r="T42" t="n">
-        <v>1810.433825013999</v>
+        <v>1779.562529327042</v>
       </c>
       <c r="U42" t="n">
-        <v>1538.50759922231</v>
+        <v>1779.562529327042</v>
       </c>
       <c r="V42" t="n">
-        <v>1538.50759922231</v>
+        <v>1493.188118022476</v>
       </c>
       <c r="W42" t="n">
-        <v>1538.50759922231</v>
+        <v>1493.188118022476</v>
       </c>
       <c r="X42" t="n">
-        <v>1246.727054327979</v>
+        <v>1493.188118022476</v>
       </c>
       <c r="Y42" t="n">
-        <v>975.6246373924901</v>
+        <v>1222.085701086987</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="C43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="D43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="E43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="F43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="G43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="H43" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="I43" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="J43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="K43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="L43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="M43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="N43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="O43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="P43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="Q43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="R43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="S43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="T43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="U43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="V43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="W43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="X43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
       <c r="Y43" t="n">
-        <v>159.0029458983529</v>
+        <v>61.28</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>851.4668757080867</v>
+        <v>851.5468757080866</v>
       </c>
       <c r="C44" t="n">
-        <v>433.8157865737493</v>
+        <v>433.8957865737493</v>
       </c>
       <c r="D44" t="n">
-        <v>433.8157865737493</v>
+        <v>433.8957865737493</v>
       </c>
       <c r="E44" t="n">
-        <v>433.8157865737493</v>
+        <v>433.8957865737493</v>
       </c>
       <c r="F44" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="G44" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="H44" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="I44" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="J44" t="n">
-        <v>460.6160489170527</v>
+        <v>61.28</v>
       </c>
       <c r="K44" t="n">
-        <v>1182.472610641805</v>
+        <v>783.1365617247528</v>
       </c>
       <c r="L44" t="n">
-        <v>1197.546002400599</v>
+        <v>1541.476561724753</v>
       </c>
       <c r="M44" t="n">
-        <v>1725.166883792851</v>
+        <v>2069.097443117004</v>
       </c>
       <c r="N44" t="n">
-        <v>2289.198640897544</v>
+        <v>2069.097443117004</v>
       </c>
       <c r="O44" t="n">
-        <v>3046.548640897561</v>
+        <v>2601.634720920271</v>
       </c>
       <c r="P44" t="n">
-        <v>3060</v>
+        <v>2615.08608002271</v>
       </c>
       <c r="Q44" t="n">
-        <v>3060</v>
+        <v>3064</v>
       </c>
       <c r="R44" t="n">
-        <v>3060</v>
+        <v>2853.072792412413</v>
       </c>
       <c r="S44" t="n">
-        <v>2679.182106115579</v>
+        <v>2853.072792412413</v>
       </c>
       <c r="T44" t="n">
-        <v>2679.182106115579</v>
+        <v>2483.359728608984</v>
       </c>
       <c r="U44" t="n">
-        <v>2059.774451614926</v>
+        <v>1863.952074108332</v>
       </c>
       <c r="V44" t="n">
-        <v>1459.924932254498</v>
+        <v>1863.952074108332</v>
       </c>
       <c r="W44" t="n">
-        <v>851.4668757080867</v>
+        <v>1863.952074108332</v>
       </c>
       <c r="X44" t="n">
-        <v>851.4668757080867</v>
+        <v>1302.051232228869</v>
       </c>
       <c r="Y44" t="n">
-        <v>851.4668757080867</v>
+        <v>1302.051232228869</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1104.443815688347</v>
+        <v>552.2104289118133</v>
       </c>
       <c r="C45" t="n">
-        <v>984.7144497659601</v>
+        <v>552.2104289118133</v>
       </c>
       <c r="D45" t="n">
-        <v>669.6258771420181</v>
+        <v>552.2104289118133</v>
       </c>
       <c r="E45" t="n">
-        <v>359.856081968369</v>
+        <v>242.4406337381642</v>
       </c>
       <c r="F45" t="n">
-        <v>359.856081968369</v>
+        <v>242.4406337381642</v>
       </c>
       <c r="G45" t="n">
-        <v>359.856081968369</v>
+        <v>242.4406337381642</v>
       </c>
       <c r="H45" t="n">
-        <v>61.2</v>
+        <v>242.4406337381642</v>
       </c>
       <c r="I45" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="J45" t="n">
-        <v>225.6249556469971</v>
+        <v>225.7049556469971</v>
       </c>
       <c r="K45" t="n">
-        <v>458.7103370243993</v>
+        <v>440.634110609305</v>
       </c>
       <c r="L45" t="n">
-        <v>776.7973910724297</v>
+        <v>758.7211646573353</v>
       </c>
       <c r="M45" t="n">
-        <v>875.8271328152889</v>
+        <v>857.7509064001945</v>
       </c>
       <c r="N45" t="n">
-        <v>1042.007426799283</v>
+        <v>1039.963117800216</v>
       </c>
       <c r="O45" t="n">
-        <v>1328.849394709418</v>
+        <v>1326.805085710349</v>
       </c>
       <c r="P45" t="n">
-        <v>1486.777822952509</v>
+        <v>1484.733513953441</v>
       </c>
       <c r="Q45" t="n">
-        <v>1486.777822952509</v>
+        <v>1484.733513953441</v>
       </c>
       <c r="R45" t="n">
-        <v>1486.777822952509</v>
+        <v>1484.733513953441</v>
       </c>
       <c r="S45" t="n">
-        <v>1486.777822952509</v>
+        <v>1484.733513953441</v>
       </c>
       <c r="T45" t="n">
-        <v>1486.777822952509</v>
+        <v>1292.027899711525</v>
       </c>
       <c r="U45" t="n">
-        <v>1486.777822952509</v>
+        <v>1292.027899711525</v>
       </c>
       <c r="V45" t="n">
-        <v>1104.443815688347</v>
+        <v>1292.027899711525</v>
       </c>
       <c r="W45" t="n">
-        <v>1104.443815688347</v>
+        <v>1292.027899711525</v>
       </c>
       <c r="X45" t="n">
-        <v>1104.443815688347</v>
+        <v>904.2877588575977</v>
       </c>
       <c r="Y45" t="n">
-        <v>1104.443815688347</v>
+        <v>904.2877588575977</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="C46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="D46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="E46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="F46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="G46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="H46" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="I46" t="n">
-        <v>61.2</v>
+        <v>61.28</v>
       </c>
       <c r="J46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="K46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="L46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="M46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="N46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="O46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="P46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="Q46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="R46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="S46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="T46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="U46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="V46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="W46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="X46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
       <c r="Y46" t="n">
-        <v>61.2</v>
+        <v>65.03294589835295</v>
       </c>
     </row>
   </sheetData>
@@ -7970,16 +7970,16 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>775.3036402309964</v>
       </c>
       <c r="M2" t="n">
-        <v>1060.271045550332</v>
+        <v>527.3206603056339</v>
       </c>
       <c r="N2" t="n">
-        <v>1096.663422488788</v>
+        <v>460.0333600798855</v>
       </c>
       <c r="O2" t="n">
-        <v>462.1276611464634</v>
+        <v>858.9916685690673</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>430.3047365861567</v>
+        <v>26.85418212448732</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L5" t="n">
-        <v>332.5983415171006</v>
+        <v>789.774351758794</v>
       </c>
       <c r="M5" t="n">
-        <v>1060.271045550332</v>
+        <v>527.3206603056339</v>
       </c>
       <c r="N5" t="n">
-        <v>1096.663422488788</v>
+        <v>81.35162862634274</v>
       </c>
       <c r="O5" t="n">
-        <v>53.99166856906732</v>
+        <v>858.9916685690673</v>
       </c>
       <c r="P5" t="n">
-        <v>792.4127685833951</v>
+        <v>791.4127685833951</v>
       </c>
       <c r="Q5" t="n">
-        <v>615.8520732695737</v>
+        <v>592.1008790735935</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,16 +8438,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>430.3047365861567</v>
+        <v>26.85418212448732</v>
       </c>
       <c r="K8" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L8" t="n">
-        <v>658.3658190815661</v>
+        <v>486.9445781590283</v>
       </c>
       <c r="M8" t="n">
-        <v>471.0768544802319</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N8" t="n">
         <v>1096.663422488788</v>
@@ -8456,10 +8456,10 @@
         <v>53.99166856906732</v>
       </c>
       <c r="P8" t="n">
-        <v>792.4127685833951</v>
+        <v>327.2291688800371</v>
       </c>
       <c r="Q8" t="n">
-        <v>162.4036692521085</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,22 +8678,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230994</v>
+        <v>175.352479127799</v>
       </c>
       <c r="L11" t="n">
-        <v>790.774351758794</v>
+        <v>789.774351758794</v>
       </c>
       <c r="M11" t="n">
-        <v>527.3206603056339</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>1096.663422488788</v>
+        <v>460.0333600798855</v>
       </c>
       <c r="O11" t="n">
-        <v>203.161717552554</v>
+        <v>53.99166856906732</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>791.4127685833951</v>
       </c>
       <c r="Q11" t="n">
         <v>615.8520732695737</v>
@@ -8924,10 +8924,10 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
-        <v>697.65743798637</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>859.9916685690673</v>
+        <v>460.9856840666492</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -9152,25 +9152,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>790.774351758794</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>460.0333600798855</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>760.2897987342229</v>
+        <v>859.9916685690673</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>317.8691330206811</v>
       </c>
       <c r="Q17" t="n">
-        <v>162.4036692521085</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>26.85418212448732</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>790.774351758794</v>
+        <v>615.5348308636537</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>1096.663422488788</v>
+        <v>460.0333600798855</v>
       </c>
       <c r="O20" t="n">
-        <v>73.66188676952466</v>
+        <v>859.9916685690673</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>792.4127685833951</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>162.4036692521085</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9629,7 +9629,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L23" t="n">
-        <v>550.9821866205548</v>
+        <v>790.774351758794</v>
       </c>
       <c r="M23" t="n">
         <v>527.3206603056339</v>
@@ -9638,10 +9638,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>53.99166856906732</v>
+        <v>606.6122720142233</v>
       </c>
       <c r="P23" t="n">
-        <v>792.4127685833951</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>615.8520732695737</v>
@@ -9860,25 +9860,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>430.3047365861567</v>
+        <v>26.85418212448732</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>602.9358490984862</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>589.9012350595167</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>53.99166856906732</v>
+        <v>819.9916685690938</v>
       </c>
       <c r="P26" t="n">
-        <v>751.4127685834191</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10097,25 +10097,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>378.5477837078026</v>
+        <v>26.85418212448732</v>
       </c>
       <c r="K29" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>750.7743517587941</v>
       </c>
       <c r="M29" t="n">
-        <v>1060.271045550332</v>
+        <v>527.3206603056339</v>
       </c>
       <c r="N29" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>53.99166856906732</v>
+        <v>819.991668569088</v>
       </c>
       <c r="P29" t="n">
-        <v>751.4127685834128</v>
+        <v>121.6851690787618</v>
       </c>
       <c r="Q29" t="n">
         <v>162.4036692521085</v>
@@ -10334,28 +10334,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>26.85418212448732</v>
       </c>
       <c r="K32" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>750.7743517587941</v>
       </c>
       <c r="M32" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>460.0333600798855</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>818.9916685690849</v>
+        <v>53.99166856906732</v>
       </c>
       <c r="P32" t="n">
-        <v>117.8374740964804</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>517.1384530861926</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10574,22 +10574,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>85.34100528691511</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>750.774351758794</v>
       </c>
       <c r="M35" t="n">
-        <v>527.3206603056339</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>1096.663422488788</v>
+        <v>460.0333600798855</v>
       </c>
       <c r="O35" t="n">
-        <v>818.9916685690847</v>
+        <v>819.9916685691038</v>
       </c>
       <c r="P35" t="n">
-        <v>731.0329144553808</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>615.8520732695737</v>
@@ -10808,7 +10808,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>26.85418212448732</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
         <v>716.8751175230994</v>
@@ -10817,16 +10817,16 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>527.3206603056339</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>762.8590052993222</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O38" t="n">
-        <v>818.9916685690849</v>
+        <v>302.6018456828107</v>
       </c>
       <c r="P38" t="n">
-        <v>751.4127685834127</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11051,19 +11051,19 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>749.774351758794</v>
+        <v>750.774351758794</v>
       </c>
       <c r="M41" t="n">
-        <v>910.4729469304376</v>
+        <v>796.649836715378</v>
       </c>
       <c r="N41" t="n">
-        <v>1096.663422488788</v>
+        <v>460.0333600798855</v>
       </c>
       <c r="O41" t="n">
-        <v>818.9916685690849</v>
+        <v>819.9916685691575</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>752.4127685834852</v>
       </c>
       <c r="Q41" t="n">
         <v>615.8520732695737</v>
@@ -11282,28 +11282,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>26.85418212448732</v>
       </c>
       <c r="K44" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>750.7743517587941</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>1029.762407660383</v>
+        <v>460.0333600798855</v>
       </c>
       <c r="O44" t="n">
-        <v>818.9916685690849</v>
+        <v>591.9081107945891</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>162.4036692521085</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -23223,16 +23223,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>136.1850884435465</v>
       </c>
       <c r="C11" t="n">
-        <v>228.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>183.3632896068686</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -23277,7 +23277,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>365.2532299697699</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -23289,10 +23289,10 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>162.128797094385</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>290.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -23399,7 +23399,7 @@
         <v>24.00059415300544</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>7.386339216372718</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23417,7 +23417,7 @@
         <v>292.8474802550089</v>
       </c>
       <c r="N13" t="n">
-        <v>343.5622555995538</v>
+        <v>12.78544695102568</v>
       </c>
       <c r="O13" t="n">
         <v>413.3283181773756</v>
@@ -23429,7 +23429,7 @@
         <v>501.215266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>185.6385011745907</v>
+        <v>503.6561607680363</v>
       </c>
       <c r="S13" t="n">
         <v>140.6192501946587</v>
@@ -23444,7 +23444,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>5.372809838709685</v>
       </c>
       <c r="X13" t="n">
         <v>26.44364543010755</v>
@@ -23478,7 +23478,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>156.481928922762</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23511,7 +23511,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>247.6495748374988</v>
       </c>
       <c r="T14" t="n">
         <v>0</v>
@@ -23520,13 +23520,13 @@
         <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>256.1141875459309</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>347.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -23645,7 +23645,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>38.49257707983156</v>
       </c>
       <c r="L16" t="n">
         <v>172.1132675020415</v>
@@ -23657,16 +23657,16 @@
         <v>319.5622555995538</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>389.3283181773756</v>
       </c>
       <c r="P16" t="n">
-        <v>382.1060652701051</v>
+        <v>437.2135366725398</v>
       </c>
       <c r="Q16" t="n">
-        <v>477.215266425598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>479.6561607680363</v>
+        <v>473.9430605339924</v>
       </c>
       <c r="S16" t="n">
         <v>116.6192501946587</v>
@@ -23882,25 +23882,25 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>2.492577079831563</v>
       </c>
       <c r="L19" t="n">
-        <v>136.1132675020415</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>232.8474802550089</v>
       </c>
       <c r="N19" t="n">
-        <v>59.53119987197073</v>
+        <v>48.19135828739408</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>353.3283181773756</v>
       </c>
       <c r="P19" t="n">
         <v>401.2135366725398</v>
       </c>
       <c r="Q19" t="n">
-        <v>441.215266425598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>443.6561607680363</v>
@@ -24119,7 +24119,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>2.492577079831563</v>
       </c>
       <c r="L22" t="n">
         <v>136.1132675020415</v>
@@ -24128,22 +24128,22 @@
         <v>232.8474802550089</v>
       </c>
       <c r="N22" t="n">
-        <v>283.5622555995537</v>
+        <v>231.5184795467486</v>
       </c>
       <c r="O22" t="n">
-        <v>353.3283181773756</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>125.42035231937</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>441.215266425598</v>
       </c>
       <c r="R22" t="n">
         <v>443.6561607680363</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>80.61925019465872</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24161,7 +24161,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>6.465352849462363</v>
       </c>
     </row>
     <row r="23">
@@ -24329,13 +24329,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>4.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -24359,25 +24359,25 @@
         <v>2.492577079831563</v>
       </c>
       <c r="L25" t="n">
-        <v>136.1132675020415</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>232.8474802550089</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>353.3283181773756</v>
       </c>
       <c r="P25" t="n">
         <v>401.2135366725398</v>
       </c>
       <c r="Q25" t="n">
-        <v>441.215266425598</v>
+        <v>291.6888569350372</v>
       </c>
       <c r="R25" t="n">
-        <v>274.3126561546289</v>
+        <v>443.6561607680363</v>
       </c>
       <c r="S25" t="n">
         <v>80.61925019465872</v>
@@ -24398,7 +24398,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>6.465352849462363</v>
       </c>
     </row>
     <row r="26">
@@ -24408,7 +24408,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>260.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -24420,7 +24420,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>183.8896287080119</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -24456,22 +24456,22 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>23.81793551171154</v>
       </c>
       <c r="S26" t="n">
-        <v>271.6495748374988</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>207.7110994934554</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>304.0240519010534</v>
+        <v>417.3734759809475</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -24566,16 +24566,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>66.11380033707866</v>
       </c>
       <c r="C28" t="n">
-        <v>51.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>64.53621805555548</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>59.98090483695654</v>
       </c>
       <c r="F28" t="n">
         <v>53.38285596774193</v>
@@ -24584,7 +24584,7 @@
         <v>24.00059415300544</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>7.386339216372704</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -24602,10 +24602,10 @@
         <v>292.8474802550089</v>
       </c>
       <c r="N28" t="n">
-        <v>343.5622555995538</v>
+        <v>113.7690808298557</v>
       </c>
       <c r="O28" t="n">
-        <v>216.0325539192554</v>
+        <v>413.3283181773756</v>
       </c>
       <c r="P28" t="n">
         <v>461.2135366725398</v>
@@ -24635,7 +24635,7 @@
         <v>26.44364543010755</v>
       </c>
       <c r="Y28" t="n">
-        <v>66.46535284946236</v>
+        <v>17.20696561867698</v>
       </c>
     </row>
     <row r="29">
@@ -24651,7 +24651,7 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>4.876562383430155</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -24708,7 +24708,7 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>0.9957623834299625</v>
       </c>
       <c r="X29" t="n">
         <v>0</v>
@@ -24836,22 +24836,22 @@
         <v>125.1132675020415</v>
       </c>
       <c r="M31" t="n">
-        <v>76.29700226366882</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>272.5622555995538</v>
+        <v>272.5622555995537</v>
       </c>
       <c r="O31" t="n">
         <v>342.3283181773756</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>390.2135366725398</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>118.7396263591656</v>
       </c>
       <c r="R31" t="n">
-        <v>432.6561607680363</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>69.61925019465872</v>
@@ -24939,7 +24939,7 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>0.9957623834297351</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -24951,7 +24951,7 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>4.876562383430041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -25076,19 +25076,19 @@
         <v>221.8474802550089</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>272.5622555995538</v>
       </c>
       <c r="O34" t="n">
-        <v>342.3283181773756</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>254.5659394526936</v>
+        <v>390.2135366725398</v>
       </c>
       <c r="Q34" t="n">
-        <v>430.215266425598</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>364.3337317835736</v>
       </c>
       <c r="S34" t="n">
         <v>69.61925019465872</v>
@@ -25125,7 +25125,7 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>4.876562383430155</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -25170,7 +25170,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>0.9957623834294509</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -25307,19 +25307,19 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>91.62466380085678</v>
+        <v>125.1132675020415</v>
       </c>
       <c r="M37" t="n">
         <v>221.8474802550089</v>
       </c>
       <c r="N37" t="n">
-        <v>272.5622555995537</v>
+        <v>272.5622555995538</v>
       </c>
       <c r="O37" t="n">
         <v>342.3283181773756</v>
       </c>
       <c r="P37" t="n">
-        <v>390.2135366725398</v>
+        <v>356.7249329713552</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -25416,7 +25416,7 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>4.876562383429871</v>
+        <v>0.995762383429792</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -25547,19 +25547,19 @@
         <v>125.1132675020415</v>
       </c>
       <c r="M40" t="n">
-        <v>78.73789660610731</v>
+        <v>221.8474802550089</v>
       </c>
       <c r="N40" t="n">
-        <v>272.5622555995538</v>
+        <v>169.4544017037104</v>
       </c>
       <c r="O40" t="n">
         <v>342.3283181773756</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>390.2135366725398</v>
       </c>
       <c r="Q40" t="n">
-        <v>430.215266425598</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -25593,28 +25593,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>40.45879983798164</v>
       </c>
       <c r="C41" t="n">
-        <v>101.9796040495852</v>
+        <v>318.4745782429939</v>
       </c>
       <c r="D41" t="n">
         <v>279.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>273.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>273.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>272.6608898749559</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>276.0215582010148</v>
       </c>
       <c r="I41" t="n">
-        <v>15.36152149172986</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -25641,13 +25641,13 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>113.8179355117115</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>361.6495748374988</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>455.2532299697699</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -25656,13 +25656,13 @@
         <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>507.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>461.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>380.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -25672,7 +25672,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>253.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>230.0999124455193</v>
@@ -25681,16 +25681,16 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>211.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>208.6362423378769</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>12.67515847281035</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -25717,7 +25717,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>35.4896801848192</v>
+        <v>35.48968018481921</v>
       </c>
       <c r="R42" t="n">
         <v>413.0686652169076</v>
@@ -25726,19 +25726,19 @@
         <v>334.605132040083</v>
       </c>
       <c r="T42" t="n">
-        <v>85.44833920520102</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>269.2069635337717</v>
       </c>
       <c r="V42" t="n">
-        <v>283.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>301.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>288.8627394453875</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -25769,10 +25769,10 @@
         <v>114.0005941530054</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5614227770032869</v>
+        <v>97.38633921637272</v>
       </c>
       <c r="I43" t="n">
-        <v>44.33194742339697</v>
+        <v>44.33194742339695</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -25787,7 +25787,7 @@
         <v>382.8474802550089</v>
       </c>
       <c r="N43" t="n">
-        <v>433.5622555995537</v>
+        <v>433.5622555995538</v>
       </c>
       <c r="O43" t="n">
         <v>503.3283181773756</v>
@@ -25805,7 +25805,7 @@
         <v>230.6192501946587</v>
       </c>
       <c r="T43" t="n">
-        <v>78.83964847347082</v>
+        <v>78.83964847347083</v>
       </c>
       <c r="U43" t="n">
         <v>19.95603061872023</v>
@@ -25830,7 +25830,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>445.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
@@ -25851,7 +25851,7 @@
         <v>371.0215582010148</v>
       </c>
       <c r="I44" t="n">
-        <v>110.3615214917299</v>
+        <v>110.3615214917298</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25878,25 +25878,25 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>208.8179355117115</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>79.63985989192179</v>
+        <v>456.6495748374988</v>
       </c>
       <c r="T44" t="n">
-        <v>550.2532299697699</v>
+        <v>184.2372968043755</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>593.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>602.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>556.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>475.3174326828064</v>
@@ -25909,13 +25909,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>348.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>206.567840182356</v>
+        <v>325.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>311.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -25927,10 +25927,10 @@
         <v>289.6879132335179</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>295.6695211486853</v>
       </c>
       <c r="I45" t="n">
-        <v>179.3490274007825</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25963,19 +25963,19 @@
         <v>429.605132040083</v>
       </c>
       <c r="T45" t="n">
-        <v>369.1496897458157</v>
+        <v>178.3711316463186</v>
       </c>
       <c r="U45" t="n">
         <v>364.2069635337717</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>378.5106671915202</v>
       </c>
       <c r="W45" t="n">
         <v>396.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>383.8627394453875</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
         <v>363.3913927661343</v>
@@ -26006,7 +26006,7 @@
         <v>209.0005941530054</v>
       </c>
       <c r="H46" t="n">
-        <v>192.3863392163727</v>
+        <v>188.6709227770033</v>
       </c>
       <c r="I46" t="n">
         <v>139.331947423397</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1174244.421733032</v>
+        <v>1174301.055541032</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2213230.480007422</v>
+        <v>2213287.113815422</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3252216.538281814</v>
+        <v>3252273.172089814</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4174874.542964242</v>
+        <v>4174533.015272687</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5132530.421349912</v>
+        <v>5132275.569213913</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6140243.091381294</v>
+        <v>6139988.239245296</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7147955.761412676</v>
+        <v>7147700.909276679</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8155668.431444059</v>
+        <v>8155413.579308062</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9064348.798650984</v>
+        <v>9064435.474206541</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10076940.88225482</v>
+        <v>10077248.330926</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11089498.88683828</v>
+        <v>11090061.18764546</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12102056.89142175</v>
+        <v>12102874.04436493</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>13114614.89600522</v>
+        <v>13115686.90108441</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13819311.77396686</v>
+        <v>13820672.71020242</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14304742.45227887</v>
+        <v>14306358.24065043</v>
       </c>
     </row>
   </sheetData>
@@ -26278,7 +26278,7 @@
         <v>1164923.76230765</v>
       </c>
       <c r="E2" t="n">
-        <v>1034523.366507458</v>
+        <v>1034237.623203458</v>
       </c>
       <c r="F2" t="n">
         <v>1073735.378796055</v>
@@ -26287,31 +26287,31 @@
         <v>1129859.660338222</v>
       </c>
       <c r="H2" t="n">
+        <v>1129859.660338221</v>
+      </c>
+      <c r="I2" t="n">
         <v>1129859.660338222</v>
       </c>
-      <c r="I2" t="n">
-        <v>1129859.660338221</v>
-      </c>
       <c r="J2" t="n">
-        <v>1022807.891043458</v>
+        <v>1023093.634347457</v>
       </c>
       <c r="K2" t="n">
-        <v>1135292.30816934</v>
+        <v>1135578.05147334</v>
       </c>
       <c r="L2" t="n">
-        <v>1135292.30816934</v>
+        <v>1135578.05147334</v>
       </c>
       <c r="M2" t="n">
-        <v>1135292.30816934</v>
+        <v>1135578.05147334</v>
       </c>
       <c r="N2" t="n">
-        <v>1135292.30816934</v>
+        <v>1135578.05147334</v>
       </c>
       <c r="O2" t="n">
-        <v>790152.8911616363</v>
+        <v>790438.6344656365</v>
       </c>
       <c r="P2" t="n">
-        <v>544270.7605316363</v>
+        <v>544556.5038356361</v>
       </c>
     </row>
     <row r="3">
@@ -26321,7 +26321,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>307112</v>
+        <v>306760</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -26333,7 +26333,7 @@
         <v>176800</v>
       </c>
       <c r="F3" t="n">
-        <v>19200</v>
+        <v>19552</v>
       </c>
       <c r="G3" t="n">
         <v>28800</v>
@@ -26357,7 +26357,7 @@
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>569257.6662584359</v>
+        <v>574259.9295586379</v>
       </c>
       <c r="C4" t="n">
-        <v>567511.8376043839</v>
+        <v>572513.3910739688</v>
       </c>
       <c r="D4" t="n">
-        <v>565763.6406247957</v>
+        <v>570764.483300834</v>
       </c>
       <c r="E4" t="n">
-        <v>484598.0359421654</v>
+        <v>489236.7646573902</v>
       </c>
       <c r="F4" t="n">
-        <v>506915.0963808019</v>
+        <v>511642.8393176598</v>
       </c>
       <c r="G4" t="n">
-        <v>539256.4162092125</v>
+        <v>543984.1591460704</v>
       </c>
       <c r="H4" t="n">
-        <v>537586.0454275212</v>
+        <v>542313.7883643791</v>
       </c>
       <c r="I4" t="n">
-        <v>535913.3427811069</v>
+        <v>540641.0857179649</v>
       </c>
       <c r="J4" t="n">
-        <v>473906.8148928646</v>
+        <v>478599.3351849837</v>
       </c>
       <c r="K4" t="n">
-        <v>539272.0325873025</v>
+        <v>543921.5906453332</v>
       </c>
       <c r="L4" t="n">
-        <v>537549.2548618037</v>
+        <v>542198.8129198344</v>
       </c>
       <c r="M4" t="n">
-        <v>535824.0148200796</v>
+        <v>540473.5728781101</v>
       </c>
       <c r="N4" t="n">
-        <v>534096.2941700573</v>
+        <v>538745.8522280878</v>
       </c>
       <c r="O4" t="n">
-        <v>329731.2089499637</v>
+        <v>334423.7292420828</v>
       </c>
       <c r="P4" t="n">
-        <v>184905.8113227512</v>
+        <v>189598.3316148702</v>
       </c>
     </row>
     <row r="5">
@@ -26425,16 +26425,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>83155.59999999999</v>
+        <v>83094.79999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>83155.59999999999</v>
+        <v>83094.79999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>83155.59999999999</v>
+        <v>83094.79999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>68107.249</v>
+        <v>68046.44899999999</v>
       </c>
       <c r="F5" t="n">
         <v>70124.905</v>
@@ -26449,25 +26449,25 @@
         <v>73151.389</v>
       </c>
       <c r="J5" t="n">
-        <v>65614.44899999999</v>
+        <v>65675.249</v>
       </c>
       <c r="K5" t="n">
-        <v>71583.348</v>
+        <v>71644.148</v>
       </c>
       <c r="L5" t="n">
-        <v>71583.348</v>
+        <v>71644.148</v>
       </c>
       <c r="M5" t="n">
-        <v>71583.348</v>
+        <v>71644.148</v>
       </c>
       <c r="N5" t="n">
-        <v>71583.348</v>
+        <v>71644.148</v>
       </c>
       <c r="O5" t="n">
-        <v>58048.239</v>
+        <v>58109.039</v>
       </c>
       <c r="P5" t="n">
-        <v>50061.684</v>
+        <v>50122.484</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>205398.4960492143</v>
+        <v>200809.0327490123</v>
       </c>
       <c r="C6" t="n">
-        <v>514256.3247032665</v>
+        <v>509315.5712336811</v>
       </c>
       <c r="D6" t="n">
-        <v>516004.5216828543</v>
+        <v>511064.4790068162</v>
       </c>
       <c r="E6" t="n">
-        <v>305018.0815652924</v>
+        <v>300154.4095460675</v>
       </c>
       <c r="F6" t="n">
-        <v>477495.3774152528</v>
+        <v>472415.6344783949</v>
       </c>
       <c r="G6" t="n">
-        <v>488651.8551290096</v>
+        <v>483924.1121921515</v>
       </c>
       <c r="H6" t="n">
-        <v>519122.2259107009</v>
+        <v>514394.4829738423</v>
       </c>
       <c r="I6" t="n">
-        <v>520794.9285571144</v>
+        <v>516067.1856202574</v>
       </c>
       <c r="J6" t="n">
-        <v>85206.62715059341</v>
+        <v>80739.05016247377</v>
       </c>
       <c r="K6" t="n">
-        <v>448436.9275820373</v>
+        <v>444012.3128280066</v>
       </c>
       <c r="L6" t="n">
-        <v>497359.7053075363</v>
+        <v>492935.0905535054</v>
       </c>
       <c r="M6" t="n">
-        <v>527884.9453492607</v>
+        <v>523460.3305952297</v>
       </c>
       <c r="N6" t="n">
-        <v>529612.6659992832</v>
+        <v>524836.0512452521</v>
       </c>
       <c r="O6" t="n">
-        <v>402373.4432116726</v>
+        <v>397905.8662235537</v>
       </c>
       <c r="P6" t="n">
-        <v>309303.2652088851</v>
+        <v>304835.6882207658</v>
       </c>
     </row>
   </sheetData>
@@ -26859,16 +26859,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C4" t="n">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D4" t="n">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E4" t="n">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="F4" t="n">
         <v>806</v>
@@ -26883,25 +26883,25 @@
         <v>806</v>
       </c>
       <c r="J4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="K4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="L4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="M4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="N4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="O4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="P4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
   </sheetData>
@@ -27008,7 +27008,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>-0</v>
@@ -27076,7 +27076,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C4" t="n">
         <v>-0</v>
@@ -27088,7 +27088,7 @@
         <v>-0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>-0</v>
@@ -27112,7 +27112,7 @@
         <v>-0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -27317,7 +27317,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -27329,7 +27329,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -27442,13 +27442,13 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>400</v>
+        <v>328.8240193868711</v>
       </c>
       <c r="F2" t="n">
         <v>400</v>
       </c>
       <c r="G2" t="n">
-        <v>324.943219386871</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -27484,10 +27484,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U2" t="n">
         <v>400</v>
@@ -27502,7 +27502,7 @@
         <v>400</v>
       </c>
       <c r="Y2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -27524,13 +27524,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
         <v>325.6879132335179</v>
       </c>
       <c r="H3" t="n">
-        <v>119.429428190628</v>
+        <v>331.6695211486853</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27560,10 +27560,10 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>400</v>
+        <v>248.1236647040658</v>
       </c>
       <c r="S3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
@@ -27597,13 +27597,13 @@
         <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
         <v>400</v>
@@ -27612,13 +27612,13 @@
         <v>228.3863392163727</v>
       </c>
       <c r="I4" t="n">
-        <v>400</v>
+        <v>242.3708757796142</v>
       </c>
       <c r="J4" t="n">
-        <v>400</v>
+        <v>32.20914555721924</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>283.4925770798316</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27645,7 +27645,7 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>269.7289741263035</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
         <v>150.9560306187202</v>
@@ -27657,7 +27657,7 @@
         <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
         <v>400</v>
@@ -27670,16 +27670,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>400</v>
@@ -27730,10 +27730,10 @@
         <v>400</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>328.8240193868712</v>
       </c>
       <c r="W5" t="n">
-        <v>324.9432193868715</v>
+        <v>400</v>
       </c>
       <c r="X5" t="n">
         <v>400</v>
@@ -27758,7 +27758,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27770,7 +27770,7 @@
         <v>331.6695211486853</v>
       </c>
       <c r="I6" t="n">
-        <v>215.3490274007825</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,13 +27794,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>166.4896801848192</v>
       </c>
       <c r="R6" t="n">
-        <v>32.7746373032831</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27815,7 +27815,7 @@
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>400</v>
+        <v>24.30608174115923</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
         <v>400</v>
@@ -27837,22 +27837,22 @@
         <v>400</v>
       </c>
       <c r="E7" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F7" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G7" t="n">
         <v>400</v>
-      </c>
-      <c r="F7" t="n">
-        <v>400</v>
-      </c>
-      <c r="G7" t="n">
-        <v>245.0005941530054</v>
       </c>
       <c r="H7" t="n">
         <v>228.3863392163727</v>
       </c>
       <c r="I7" t="n">
-        <v>175.331947423397</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>269.0051069979516</v>
+        <v>233.9598328386747</v>
       </c>
       <c r="K7" t="n">
         <v>283.4925770798316</v>
@@ -27879,10 +27879,10 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>361.6192501946587</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>400</v>
+        <v>209.8396484734708</v>
       </c>
       <c r="U7" t="n">
         <v>400</v>
@@ -27891,13 +27891,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27910,7 +27910,7 @@
         <v>400</v>
       </c>
       <c r="C8" t="n">
-        <v>80.12528387515908</v>
+        <v>400</v>
       </c>
       <c r="D8" t="n">
         <v>400</v>
@@ -27922,13 +27922,13 @@
         <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>146.3615214917299</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,19 +27955,19 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>244.8179355117115</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
         <v>400</v>
       </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
       <c r="U8" t="n">
-        <v>400</v>
+        <v>182.4624978951411</v>
       </c>
       <c r="V8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>400</v>
@@ -27995,19 +27995,19 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>148.5932966782534</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>325.6879132335179</v>
       </c>
       <c r="H9" t="n">
-        <v>331.6695211486853</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>215.3490274007825</v>
+        <v>13.30350566793199</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28034,7 +28034,7 @@
         <v>166.4896801848192</v>
       </c>
       <c r="R9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
@@ -28049,7 +28049,7 @@
         <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
@@ -28065,10 +28065,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
         <v>285.5362180555555</v>
@@ -28080,19 +28080,19 @@
         <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>245.0005941530054</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>228.3863392163727</v>
+        <v>336.0998095571378</v>
       </c>
       <c r="I10" t="n">
         <v>400</v>
       </c>
       <c r="J10" t="n">
+        <v>32.20914555721924</v>
+      </c>
+      <c r="K10" t="n">
         <v>400</v>
-      </c>
-      <c r="K10" t="n">
-        <v>283.4925770798316</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,22 +28116,22 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>400</v>
+        <v>361.6192501946587</v>
       </c>
       <c r="T10" t="n">
         <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>181.1610770588206</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
         <v>287.4653528494624</v>
@@ -28244,13 +28244,13 @@
         <v>221</v>
       </c>
       <c r="I12" t="n">
-        <v>215.3490274007825</v>
+        <v>221</v>
       </c>
       <c r="J12" t="n">
+        <v>80.38481947928386</v>
+      </c>
+      <c r="K12" t="n">
         <v>221</v>
-      </c>
-      <c r="K12" t="n">
-        <v>31.52547226332138</v>
       </c>
       <c r="L12" t="n">
         <v>221</v>
@@ -28268,7 +28268,7 @@
         <v>221</v>
       </c>
       <c r="Q12" t="n">
-        <v>221</v>
+        <v>166.4896801848192</v>
       </c>
       <c r="R12" t="n">
         <v>221</v>
@@ -28481,13 +28481,13 @@
         <v>245</v>
       </c>
       <c r="I15" t="n">
+        <v>215.3490274007825</v>
+      </c>
+      <c r="J15" t="n">
+        <v>64.72633385995303</v>
+      </c>
+      <c r="K15" t="n">
         <v>245</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -28496,16 +28496,16 @@
         <v>245</v>
       </c>
       <c r="N15" t="n">
-        <v>201.5650414455549</v>
+        <v>245</v>
       </c>
       <c r="O15" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>245</v>
       </c>
       <c r="Q15" t="n">
-        <v>245</v>
+        <v>166.4896801848192</v>
       </c>
       <c r="R15" t="n">
         <v>245</v>
@@ -28633,10 +28633,10 @@
         <v>281</v>
       </c>
       <c r="G17" t="n">
+        <v>280.7637623834296</v>
+      </c>
+      <c r="H17" t="n">
         <v>281</v>
-      </c>
-      <c r="H17" t="n">
-        <v>280.7637623834296</v>
       </c>
       <c r="I17" t="n">
         <v>146.3615214917299</v>
@@ -28727,10 +28727,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="M18" t="n">
-        <v>281</v>
+        <v>212.7621465321286</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -28739,7 +28739,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>212.7621465321287</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>166.4896801848192</v>
@@ -28876,7 +28876,7 @@
         <v>281</v>
       </c>
       <c r="I20" t="n">
-        <v>146.3615214917299</v>
+        <v>146.1252838751595</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28906,7 +28906,7 @@
         <v>244.8179355117115</v>
       </c>
       <c r="S20" t="n">
-        <v>280.7637623834296</v>
+        <v>281</v>
       </c>
       <c r="T20" t="n">
         <v>281</v>
@@ -28961,22 +28961,22 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>212.7621465321287</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>212.7621465321289</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>166.4896801848192</v>
@@ -29113,7 +29113,7 @@
         <v>281</v>
       </c>
       <c r="I23" t="n">
-        <v>146.3615214917299</v>
+        <v>146.1252838751595</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>244.5816978951411</v>
+        <v>244.8179355117115</v>
       </c>
       <c r="S23" t="n">
         <v>281</v>
@@ -29198,22 +29198,22 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
+        <v>212.7621465321289</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>281</v>
-      </c>
-      <c r="L24" t="n">
-        <v>212.7621465321287</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>166.4896801848192</v>
@@ -29429,7 +29429,7 @@
         <v>221</v>
       </c>
       <c r="I27" t="n">
-        <v>221</v>
+        <v>215.3490274007825</v>
       </c>
       <c r="J27" t="n">
         <v>221</v>
@@ -29444,7 +29444,7 @@
         <v>221</v>
       </c>
       <c r="N27" t="n">
-        <v>25.87449966410324</v>
+        <v>31.52547226332064</v>
       </c>
       <c r="O27" t="n">
         <v>221</v>
@@ -29678,10 +29678,10 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>248.7610055827432</v>
       </c>
       <c r="N30" t="n">
-        <v>123.2506857675625</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>292</v>
+        <v>166.4896801848192</v>
       </c>
       <c r="R30" t="n">
         <v>292</v>
@@ -29912,7 +29912,7 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>199.9016583667799</v>
+        <v>33.41197818196076</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -29924,10 +29924,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="Q33" t="n">
-        <v>292</v>
+        <v>166.4896801848192</v>
       </c>
       <c r="R33" t="n">
         <v>292</v>
@@ -30149,7 +30149,7 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>33.41197818196054</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -30161,7 +30161,7 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>33.41197818196059</v>
       </c>
       <c r="Q36" t="n">
         <v>166.4896801848192</v>
@@ -30383,10 +30383,10 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>33.41197818196082</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>33.41197818196065</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -30395,10 +30395,10 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>292</v>
       </c>
       <c r="P39" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>166.4896801848192</v>
@@ -30617,13 +30617,13 @@
         <v>131</v>
       </c>
       <c r="J42" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>131</v>
       </c>
       <c r="L42" t="n">
-        <v>64.26415094339623</v>
+        <v>131</v>
       </c>
       <c r="M42" t="n">
         <v>131</v>
@@ -30635,7 +30635,7 @@
         <v>131</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>120.1835025147816</v>
       </c>
       <c r="Q42" t="n">
         <v>131</v>
@@ -30696,7 +30696,7 @@
         <v>131</v>
       </c>
       <c r="J43" t="n">
-        <v>131</v>
+        <v>32.20914555721924</v>
       </c>
       <c r="K43" t="n">
         <v>131</v>
@@ -30857,7 +30857,7 @@
         <v>36</v>
       </c>
       <c r="K45" t="n">
-        <v>36</v>
+        <v>17.66037735849057</v>
       </c>
       <c r="L45" t="n">
         <v>36</v>
@@ -30866,7 +30866,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>19.80614402421552</v>
+        <v>36</v>
       </c>
       <c r="O45" t="n">
         <v>36</v>
@@ -30933,7 +30933,7 @@
         <v>36</v>
       </c>
       <c r="J46" t="n">
-        <v>32.20914555721924</v>
+        <v>36</v>
       </c>
       <c r="K46" t="n">
         <v>36</v>
@@ -34743,22 +34743,22 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>403.4505544616694</v>
+        <v>691.8096165335973</v>
       </c>
       <c r="K2" t="n">
-        <v>729.1480421462151</v>
+        <v>805</v>
       </c>
       <c r="L2" t="n">
-        <v>71.46945406664349</v>
+        <v>805</v>
       </c>
       <c r="M2" t="n">
-        <v>532.9503852446986</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>636.6300624089025</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>408.1359925773961</v>
+        <v>805</v>
       </c>
       <c r="P2" t="n">
         <v>13.58723141660502</v>
@@ -34883,13 +34883,13 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
         <v>154.9994058469946</v>
@@ -34898,13 +34898,13 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>224.668052576603</v>
+        <v>67.03892835621721</v>
       </c>
       <c r="J4" t="n">
-        <v>367.7908544427808</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>116.5074229201684</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34931,7 +34931,7 @@
         <v>38.38074980534128</v>
       </c>
       <c r="T4" t="n">
-        <v>59.88932565283271</v>
+        <v>190.1603515265292</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -34943,7 +34943,7 @@
         <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
         <v>112.5346471505376</v>
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>403.4505544616694</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>12.27292462311556</v>
+        <v>729.1480421462149</v>
       </c>
       <c r="L5" t="n">
-        <v>404.0677955837357</v>
+        <v>805</v>
       </c>
       <c r="M5" t="n">
-        <v>532.9503852446986</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>636.6300624089025</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>805</v>
       </c>
       <c r="P5" t="n">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="Q5" t="n">
-        <v>453.4484040174651</v>
+        <v>429.697209821485</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,7 +35114,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
         <v>127.2747533519553</v>
@@ -35123,22 +35123,22 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>154.9994058469946</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>224.668052576603</v>
       </c>
       <c r="J7" t="n">
-        <v>236.7959614407324</v>
+        <v>201.7506872814555</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -35165,10 +35165,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>38.38074980534128</v>
       </c>
       <c r="T7" t="n">
-        <v>190.1603515265292</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>249.0439693812798</v>
@@ -35177,13 +35177,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35217,16 +35217,16 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>403.4505544616694</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>729.1480421462151</v>
+        <v>805</v>
       </c>
       <c r="L8" t="n">
-        <v>673.5914673227721</v>
+        <v>804.9999999999998</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>532.9503852446986</v>
       </c>
       <c r="N8" t="n">
         <v>636.6300624089025</v>
@@ -35235,10 +35235,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>806</v>
+        <v>340.8164002966421</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>453.4484040174651</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,10 +35351,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -35366,19 +35366,19 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>154.9994058469946</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>107.7134703407651</v>
       </c>
       <c r="I10" t="n">
         <v>224.668052576603</v>
       </c>
       <c r="J10" t="n">
-        <v>367.7908544427808</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>116.5074229201684</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,22 +35402,22 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>38.38074980534128</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>190.1603515265292</v>
       </c>
       <c r="U10" t="n">
-        <v>30.20504644010036</v>
+        <v>249.0439693812798</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -35457,22 +35457,22 @@
         <v>403.4505544616694</v>
       </c>
       <c r="K11" t="n">
-        <v>729.1480421462151</v>
+        <v>187.6254037509146</v>
       </c>
       <c r="L11" t="n">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>532.9503852446986</v>
       </c>
       <c r="N11" t="n">
-        <v>636.6300624089025</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>149.1700489834867</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>13.58723141660502</v>
+        <v>805</v>
       </c>
       <c r="Q11" t="n">
         <v>453.4484040174651</v>
@@ -35530,13 +35530,13 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>5.650972599217504</v>
       </c>
       <c r="J12" t="n">
-        <v>351.0858137848455</v>
+        <v>210.4706332641294</v>
       </c>
       <c r="K12" t="n">
-        <v>230.9652514324145</v>
+        <v>420.4397791690932</v>
       </c>
       <c r="L12" t="n">
         <v>506.30005459397</v>
@@ -35554,7 +35554,7 @@
         <v>344.5236648920117</v>
       </c>
       <c r="Q12" t="n">
-        <v>54.51031981518079</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35703,10 +35703,10 @@
         <v>532.9503852446986</v>
       </c>
       <c r="N14" t="n">
-        <v>237.6240779064845</v>
+        <v>636.6300624089025</v>
       </c>
       <c r="O14" t="n">
-        <v>806</v>
+        <v>406.9940154975819</v>
       </c>
       <c r="P14" t="n">
         <v>13.58723141660502</v>
@@ -35767,13 +35767,13 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>29.6509725992175</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>130.0858137848455</v>
+        <v>194.8121476447986</v>
       </c>
       <c r="K15" t="n">
-        <v>199.4397791690932</v>
+        <v>444.4397791690932</v>
       </c>
       <c r="L15" t="n">
         <v>285.30005459397</v>
@@ -35782,16 +35782,16 @@
         <v>345.0300421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>349.617780233455</v>
+        <v>393.0527387879001</v>
       </c>
       <c r="O15" t="n">
-        <v>498.7393615253879</v>
+        <v>253.7393615253879</v>
       </c>
       <c r="P15" t="n">
         <v>368.5236648920117</v>
       </c>
       <c r="Q15" t="n">
-        <v>78.51031981518079</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35931,25 +35931,25 @@
         <v>403.4505544616694</v>
       </c>
       <c r="K17" t="n">
-        <v>729.1480421462151</v>
+        <v>12.27292462311556</v>
       </c>
       <c r="L17" t="n">
-        <v>806</v>
+        <v>15.22564824120604</v>
       </c>
       <c r="M17" t="n">
         <v>532.9503852446986</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>636.6300624089025</v>
       </c>
       <c r="O17" t="n">
-        <v>706.2981301651556</v>
+        <v>806</v>
       </c>
       <c r="P17" t="n">
-        <v>13.58723141660502</v>
+        <v>331.4563644372861</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>453.4484040174651</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36013,10 +36013,10 @@
         <v>199.4397791690932</v>
       </c>
       <c r="L18" t="n">
-        <v>285.30005459397</v>
+        <v>566.30005459397</v>
       </c>
       <c r="M18" t="n">
-        <v>381.0300421645043</v>
+        <v>312.7921886966328</v>
       </c>
       <c r="N18" t="n">
         <v>148.0527387879001</v>
@@ -36025,7 +36025,7 @@
         <v>253.7393615253879</v>
       </c>
       <c r="P18" t="n">
-        <v>336.2858114241404</v>
+        <v>123.5236648920117</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -36080,7 +36080,7 @@
         <v>35.99940584699456</v>
       </c>
       <c r="H19" t="n">
-        <v>52.61366078362728</v>
+        <v>52.6136607836273</v>
       </c>
       <c r="I19" t="n">
         <v>105.668052576603</v>
@@ -36116,7 +36116,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>71.16035152652917</v>
+        <v>71.16035152652918</v>
       </c>
       <c r="U19" t="n">
         <v>130.0439693812798</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>403.4505544616694</v>
       </c>
       <c r="K20" t="n">
-        <v>729.1480421462149</v>
+        <v>12.27292462311556</v>
       </c>
       <c r="L20" t="n">
-        <v>806</v>
+        <v>630.7604791048598</v>
       </c>
       <c r="M20" t="n">
         <v>532.9503852446986</v>
       </c>
       <c r="N20" t="n">
-        <v>636.6300624089025</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>19.67021820045733</v>
+        <v>806</v>
       </c>
       <c r="P20" t="n">
-        <v>13.58723141660502</v>
+        <v>806</v>
       </c>
       <c r="Q20" t="n">
-        <v>453.4484040174651</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36247,22 +36247,22 @@
         <v>130.0858137848455</v>
       </c>
       <c r="K21" t="n">
-        <v>199.4397791690932</v>
+        <v>412.2019257012218</v>
       </c>
       <c r="L21" t="n">
-        <v>285.30005459397</v>
+        <v>566.30005459397</v>
       </c>
       <c r="M21" t="n">
         <v>100.0300421645043</v>
       </c>
       <c r="N21" t="n">
-        <v>360.814885320029</v>
+        <v>148.0527387879001</v>
       </c>
       <c r="O21" t="n">
         <v>253.7393615253879</v>
       </c>
       <c r="P21" t="n">
-        <v>404.5236648920117</v>
+        <v>123.5236648920117</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -36408,7 +36408,7 @@
         <v>729.1480421462149</v>
       </c>
       <c r="L23" t="n">
-        <v>566.2078348617608</v>
+        <v>806</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -36417,10 +36417,10 @@
         <v>636.6300624089025</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>552.620603445156</v>
       </c>
       <c r="P23" t="n">
-        <v>806</v>
+        <v>13.58723141660502</v>
       </c>
       <c r="Q23" t="n">
         <v>453.4484040174651</v>
@@ -36484,10 +36484,10 @@
         <v>130.0858137848455</v>
       </c>
       <c r="K24" t="n">
-        <v>480.4397791690932</v>
+        <v>412.201925701222</v>
       </c>
       <c r="L24" t="n">
-        <v>498.0622011260987</v>
+        <v>285.30005459397</v>
       </c>
       <c r="M24" t="n">
         <v>100.0300421645043</v>
@@ -36499,7 +36499,7 @@
         <v>253.7393615253879</v>
       </c>
       <c r="P24" t="n">
-        <v>123.5236648920117</v>
+        <v>404.5236648920117</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -36554,7 +36554,7 @@
         <v>35.99940584699456</v>
       </c>
       <c r="H25" t="n">
-        <v>52.6136607836273</v>
+        <v>52.61366078362728</v>
       </c>
       <c r="I25" t="n">
         <v>105.668052576603</v>
@@ -36590,7 +36590,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>71.16035152652918</v>
+        <v>71.16035152652917</v>
       </c>
       <c r="U25" t="n">
         <v>130.0439693812798</v>
@@ -36639,25 +36639,25 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>403.4505544616694</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>729.1480421462149</v>
+        <v>12.27292462311558</v>
       </c>
       <c r="L26" t="n">
-        <v>15.22564824120604</v>
+        <v>618.1614973396922</v>
       </c>
       <c r="M26" t="n">
         <v>532.9503852446986</v>
       </c>
       <c r="N26" t="n">
-        <v>129.8678749796312</v>
+        <v>636.6300624089025</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>766.0000000000265</v>
       </c>
       <c r="P26" t="n">
-        <v>765.000000000024</v>
+        <v>13.58723141660502</v>
       </c>
       <c r="Q26" t="n">
         <v>453.4484040174651</v>
@@ -36715,7 +36715,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>5.650972599217504</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>351.0858137848455</v>
@@ -36730,7 +36730,7 @@
         <v>321.0300421645043</v>
       </c>
       <c r="N27" t="n">
-        <v>173.9272384520034</v>
+        <v>179.5782110512208</v>
       </c>
       <c r="O27" t="n">
         <v>474.7393615253879</v>
@@ -36739,7 +36739,7 @@
         <v>344.5236648920117</v>
       </c>
       <c r="Q27" t="n">
-        <v>54.51031981518079</v>
+        <v>54.5103198151808</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36794,7 +36794,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>45.66805257660304</v>
+        <v>45.66805257660303</v>
       </c>
       <c r="J28" t="n">
         <v>188.7908544427808</v>
@@ -36827,7 +36827,7 @@
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>11.16035152652917</v>
+        <v>11.16035152652918</v>
       </c>
       <c r="U28" t="n">
         <v>70.04396938127977</v>
@@ -36876,25 +36876,25 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>351.6936015833153</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>765.0000000000001</v>
+        <v>729.1480421462149</v>
       </c>
       <c r="L29" t="n">
-        <v>56.04954997690152</v>
+        <v>766.0000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>532.9503852446986</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>636.6300624089025</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>766.0000000000207</v>
       </c>
       <c r="P29" t="n">
-        <v>765.0000000000177</v>
+        <v>135.2724004953668</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -36952,7 +36952,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>76.65097259921751</v>
+        <v>76.6509725992175</v>
       </c>
       <c r="J30" t="n">
         <v>130.0858137848455</v>
@@ -36964,10 +36964,10 @@
         <v>285.30005459397</v>
       </c>
       <c r="M30" t="n">
-        <v>100.0300421645043</v>
+        <v>348.7910477472475</v>
       </c>
       <c r="N30" t="n">
-        <v>271.3034245554626</v>
+        <v>148.0527387879001</v>
       </c>
       <c r="O30" t="n">
         <v>253.7393615253879</v>
@@ -36976,7 +36976,7 @@
         <v>123.5236648920117</v>
       </c>
       <c r="Q30" t="n">
-        <v>125.5103198151808</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37028,7 +37028,7 @@
         <v>46.99940584699456</v>
       </c>
       <c r="H31" t="n">
-        <v>63.61366078362728</v>
+        <v>63.6136607836273</v>
       </c>
       <c r="I31" t="n">
         <v>116.668052576603</v>
@@ -37064,7 +37064,7 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>82.16035152652917</v>
+        <v>82.16035152652918</v>
       </c>
       <c r="U31" t="n">
         <v>141.0439693812798</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>403.4505544616694</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>765</v>
+        <v>729.1480421462149</v>
       </c>
       <c r="L32" t="n">
-        <v>56.04954997696859</v>
+        <v>766.0000000000001</v>
       </c>
       <c r="M32" t="n">
         <v>532.9503852446986</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>636.6300624089025</v>
       </c>
       <c r="O32" t="n">
-        <v>765.0000000000176</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>131.4247055130854</v>
+        <v>13.58723141660502</v>
       </c>
       <c r="Q32" t="n">
-        <v>453.4484040174651</v>
+        <v>354.7347838340841</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37198,7 +37198,7 @@
         <v>199.4397791690932</v>
       </c>
       <c r="L33" t="n">
-        <v>485.2017129607499</v>
+        <v>318.7120327759308</v>
       </c>
       <c r="M33" t="n">
         <v>100.0300421645043</v>
@@ -37210,10 +37210,10 @@
         <v>253.7393615253879</v>
       </c>
       <c r="P33" t="n">
-        <v>123.5236648920117</v>
+        <v>415.5236648920117</v>
       </c>
       <c r="Q33" t="n">
-        <v>125.5103198151808</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37353,22 +37353,22 @@
         <v>403.4505544616694</v>
       </c>
       <c r="K35" t="n">
-        <v>88.94878421290144</v>
+        <v>97.61392991003072</v>
       </c>
       <c r="L35" t="n">
-        <v>15.22564824120604</v>
+        <v>766</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>532.9503852446986</v>
       </c>
       <c r="N35" t="n">
-        <v>636.6300624089025</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>765.0000000000174</v>
+        <v>766.0000000000365</v>
       </c>
       <c r="P35" t="n">
-        <v>744.6201458719859</v>
+        <v>13.58723141660502</v>
       </c>
       <c r="Q35" t="n">
         <v>453.4484040174651</v>
@@ -37435,7 +37435,7 @@
         <v>199.4397791690932</v>
       </c>
       <c r="L36" t="n">
-        <v>318.7120327759305</v>
+        <v>285.30005459397</v>
       </c>
       <c r="M36" t="n">
         <v>100.0300421645043</v>
@@ -37447,7 +37447,7 @@
         <v>253.7393615253879</v>
       </c>
       <c r="P36" t="n">
-        <v>123.5236648920117</v>
+        <v>156.9356430739723</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -37502,7 +37502,7 @@
         <v>46.99940584699456</v>
       </c>
       <c r="H37" t="n">
-        <v>63.6136607836273</v>
+        <v>63.61366078362728</v>
       </c>
       <c r="I37" t="n">
         <v>116.668052576603</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>82.16035152652918</v>
+        <v>82.16035152652917</v>
       </c>
       <c r="U37" t="n">
         <v>141.0439693812798</v>
@@ -37587,25 +37587,25 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>403.4505544616694</v>
       </c>
       <c r="K38" t="n">
-        <v>765</v>
+        <v>729.1480421462152</v>
       </c>
       <c r="L38" t="n">
-        <v>56.04954997703578</v>
+        <v>15.22564824120604</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>532.9503852446986</v>
       </c>
       <c r="N38" t="n">
-        <v>302.8256452194369</v>
+        <v>636.6300624089025</v>
       </c>
       <c r="O38" t="n">
-        <v>765.0000000000176</v>
+        <v>248.6101771137434</v>
       </c>
       <c r="P38" t="n">
-        <v>765.0000000000176</v>
+        <v>13.58723141660502</v>
       </c>
       <c r="Q38" t="n">
         <v>453.4484040174651</v>
@@ -37669,10 +37669,10 @@
         <v>130.0858137848455</v>
       </c>
       <c r="K39" t="n">
-        <v>232.851757351054</v>
+        <v>199.4397791690932</v>
       </c>
       <c r="L39" t="n">
-        <v>285.30005459397</v>
+        <v>318.7120327759307</v>
       </c>
       <c r="M39" t="n">
         <v>100.0300421645043</v>
@@ -37681,10 +37681,10 @@
         <v>148.0527387879001</v>
       </c>
       <c r="O39" t="n">
-        <v>253.7393615253879</v>
+        <v>545.7393615253879</v>
       </c>
       <c r="P39" t="n">
-        <v>415.5236648920117</v>
+        <v>123.5236648920117</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37827,22 +37827,22 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>12.27292462311557</v>
+        <v>12.27292462311558</v>
       </c>
       <c r="L41" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="M41" t="n">
-        <v>383.1522866248038</v>
+        <v>269.3291764097442</v>
       </c>
       <c r="N41" t="n">
-        <v>636.6300624089025</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>765.0000000000176</v>
+        <v>766.0000000000902</v>
       </c>
       <c r="P41" t="n">
-        <v>13.58723141660502</v>
+        <v>766.0000000000902</v>
       </c>
       <c r="Q41" t="n">
         <v>453.4484040174651</v>
@@ -37903,13 +37903,13 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>261.0858137848455</v>
+        <v>130.0858137848455</v>
       </c>
       <c r="K42" t="n">
         <v>330.4397791690932</v>
       </c>
       <c r="L42" t="n">
-        <v>349.5642055373663</v>
+        <v>416.30005459397</v>
       </c>
       <c r="M42" t="n">
         <v>231.0300421645043</v>
@@ -37921,7 +37921,7 @@
         <v>384.7393615253879</v>
       </c>
       <c r="P42" t="n">
-        <v>123.5236648920117</v>
+        <v>243.7071674067932</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -37982,7 +37982,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>98.79085444278076</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38061,28 +38061,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>403.4505544616694</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>729.1480421462149</v>
       </c>
       <c r="L44" t="n">
-        <v>15.22564824120604</v>
+        <v>766.0000000000001</v>
       </c>
       <c r="M44" t="n">
         <v>532.9503852446986</v>
       </c>
       <c r="N44" t="n">
-        <v>569.7290475804975</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>765.0000000000176</v>
+        <v>537.9164422255218</v>
       </c>
       <c r="P44" t="n">
         <v>13.58723141660502</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>453.4484040174651</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38143,7 +38143,7 @@
         <v>166.0858137848455</v>
       </c>
       <c r="K45" t="n">
-        <v>235.4397791690932</v>
+        <v>217.1001565275837</v>
       </c>
       <c r="L45" t="n">
         <v>321.30005459397</v>
@@ -38152,7 +38152,7 @@
         <v>100.0300421645043</v>
       </c>
       <c r="N45" t="n">
-        <v>167.8588828121156</v>
+        <v>184.0527387879001</v>
       </c>
       <c r="O45" t="n">
         <v>289.7393615253879</v>
@@ -38219,7 +38219,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>3.790854442780756</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
